--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC31" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Argentina_" displayName="AveragesTable_Argentina_" ref="A1:EC31" headerRowCount="1">
   <autoFilter ref="A1:EC31"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.94</v>
+        <v>49.88</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.06</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.78</v>
+        <v>50.75</v>
       </c>
       <c r="DW9" t="n">
         <v>0.09</v>
@@ -5048,7 +5048,7 @@
         <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>15.5</v>
+        <v>15.44</v>
       </c>
       <c r="Q11" t="n">
         <v>11.19</v>
@@ -5360,7 +5360,7 @@
         <v>1.32</v>
       </c>
       <c r="DP11" t="n">
-        <v>15.1</v>
+        <v>15.06</v>
       </c>
       <c r="DQ11" t="n">
         <v>10.32</v>
@@ -5878,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>48</v>
+        <v>48.06</v>
       </c>
       <c r="Y13" t="n">
         <v>0.19</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.03</v>
+        <v>46.06</v>
       </c>
       <c r="DW13" t="n">
         <v>0.13</v>
@@ -7143,7 +7143,7 @@
         <v>11.18</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.71</v>
+        <v>14.65</v>
       </c>
       <c r="AS16" t="n">
         <v>7.18</v>
@@ -7370,7 +7370,7 @@
         <v>10.62</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.53</v>
+        <v>15.5</v>
       </c>
       <c r="DR16" t="n">
         <v>6.42</v>
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>47.5</v>
+        <v>47.56</v>
       </c>
       <c r="Y17" t="n">
         <v>0.44</v>
@@ -7788,7 +7788,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>45.66</v>
+        <v>45.68</v>
       </c>
       <c r="DW17" t="n">
         <v>0.25</v>
@@ -13177,7 +13177,7 @@
         <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>50.69</v>
+        <v>50.62</v>
       </c>
       <c r="AZ31" t="n">
         <v>0.31</v>
@@ -13398,7 +13398,7 @@
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>55.29</v>
+        <v>55.26</v>
       </c>
       <c r="DW31" t="n">
         <v>0.29</v>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
         <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
         <v>0.19</v>
@@ -2275,52 +2275,52 @@
         <v>2.94</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AI4" t="n">
-        <v>94.87</v>
+        <v>96.88</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>45.53</v>
+        <v>45.69</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.2</v>
+        <v>12.56</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.67</v>
+        <v>10.44</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>47.6</v>
+        <v>47.06</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.4</v>
+        <v>6.81</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="BD4" t="n">
-        <v>20.13</v>
+        <v>19.88</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.9</v>
+        <v>8.75</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="BJ4" t="n">
         <v>0.84</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.26</v>
+        <v>4.16</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.65</v>
+        <v>4.59</v>
       </c>
       <c r="BR4" t="n">
-        <v>96.77</v>
+        <v>96.88</v>
       </c>
       <c r="BS4" t="n">
-        <v>70.97</v>
+        <v>71.88</v>
       </c>
       <c r="BT4" t="n">
-        <v>45.16</v>
+        <v>46.88</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.13</v>
+        <v>18.75</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>38.71</v>
+        <v>40.62</v>
       </c>
       <c r="BY4" t="n">
         <v>2.33</v>
@@ -2416,22 +2416,22 @@
         <v>2.59</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="CE4" t="n">
         <v>1.55</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CG4" t="n">
         <v>2.34</v>
@@ -2452,16 +2452,16 @@
         <v>2.16</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO4" t="n">
         <v>1.53</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CQ4" t="n">
         <v>5.06</v>
@@ -2482,7 +2482,7 @@
         <v>1.67</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CX4" t="n">
         <v>1.72</v>
@@ -2500,13 +2500,13 @@
         <v>1.58</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.82</v>
+        <v>5.75</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF4" t="n">
         <v>1.84</v>
@@ -2515,37 +2515,37 @@
         <v>2.13</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.36</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.42</v>
+        <v>4.37</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM4" t="n">
-        <v>47.58</v>
+        <v>47.6</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.97</v>
+        <v>13.12</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.78</v>
+        <v>10.66</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.19</v>
+        <v>8.09</v>
       </c>
       <c r="DS4" t="n">
         <v>0.03</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>48.03</v>
+        <v>47.75</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.71</v>
+        <v>10.94</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.65</v>
+        <v>6.84</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.51</v>
+        <v>18.44</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="5">
@@ -8218,94 +8218,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
         <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F19" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="G19" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="H19" t="n">
-        <v>95.73</v>
+        <v>95.69</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="K19" t="n">
-        <v>4.13</v>
+        <v>3.94</v>
       </c>
       <c r="L19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="M19" t="n">
-        <v>49.33</v>
+        <v>48.19</v>
       </c>
       <c r="N19" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="O19" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="P19" t="n">
-        <v>11.4</v>
+        <v>11.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.6</v>
+        <v>12.94</v>
       </c>
       <c r="R19" t="n">
-        <v>6.93</v>
+        <v>7.19</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="U19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="V19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>50.67</v>
+        <v>51.31</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.87</v>
+        <v>11.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>7</v>
+        <v>6.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.87</v>
+        <v>5.06</v>
       </c>
       <c r="AC19" t="n">
-        <v>20.93</v>
+        <v>20.44</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
         <v>0.12</v>
@@ -8389,70 +8389,70 @@
         <v>2.18</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.279999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN19" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.97</v>
+        <v>4.91</v>
       </c>
       <c r="BR19" t="n">
-        <v>81.25</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>56.25</v>
+        <v>57.58</v>
       </c>
       <c r="BT19" t="n">
-        <v>21.88</v>
+        <v>24.24</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.12</v>
+        <v>6.06</v>
       </c>
       <c r="BV19" t="n">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>37.5</v>
+        <v>39.39</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="CA19" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="CC19" t="n">
         <v>3.26</v>
@@ -8464,7 +8464,7 @@
         <v>1.63</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CG19" t="n">
         <v>2.24</v>
@@ -8476,7 +8476,7 @@
         <v>1.56</v>
       </c>
       <c r="CJ19" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CK19" t="n">
         <v>1.73</v>
@@ -8494,10 +8494,10 @@
         <v>1.61</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CQ19" t="n">
-        <v>6.12</v>
+        <v>6.07</v>
       </c>
       <c r="CR19" t="n">
         <v>1.72</v>
@@ -8508,10 +8508,10 @@
       </c>
       <c r="CU19" t="inlineStr"/>
       <c r="CV19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CX19" t="n">
         <v>1.88</v>
@@ -8526,55 +8526,55 @@
         <v>1.57</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DC19" t="n">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
       <c r="DD19" t="n">
-        <v>7.12</v>
+        <v>6.94</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="DH19" t="n">
-        <v>96.16</v>
+        <v>96.12</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.28</v>
+        <v>4.18</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM19" t="n">
-        <v>49.56</v>
+        <v>49</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.22</v>
+        <v>11.09</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.19</v>
+        <v>12.36</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.220000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DS19" t="n">
         <v>0.09</v>
@@ -8586,28 +8586,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>50.91</v>
+        <v>51.21</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.16</v>
+        <v>11.18</v>
       </c>
       <c r="DY19" t="n">
-        <v>7</v>
+        <v>6.91</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.16</v>
+        <v>4.27</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.5</v>
+        <v>20.28</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -2714,7 +2714,7 @@
         <v>14.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.81</v>
+        <v>12.88</v>
       </c>
       <c r="AS5" t="n">
         <v>8.94</v>
@@ -2945,7 +2945,7 @@
         <v>13.78</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.12</v>
+        <v>13.16</v>
       </c>
       <c r="DR5" t="n">
         <v>7.72</v>
@@ -3219,13 +3219,13 @@
         <v>3.3</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CA6" t="n">
         <v>3.07</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CC6" t="n">
         <v>5.09</v>
@@ -3273,13 +3273,13 @@
         <v>5.39</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CS6" t="n">
         <v>3.31</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CU6" t="n">
         <v>1.35</v>
@@ -3303,10 +3303,10 @@
         <v>1.58</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="DD6" t="n">
         <v>6.06</v>
@@ -3682,7 +3682,7 @@
         <v>3.24</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CU7" t="n">
         <v>1.36</v>
@@ -3691,13 +3691,13 @@
         <v>1.65</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.12</v>
@@ -3869,10 +3869,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.06</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.94</v>
+        <v>7.89</v>
       </c>
       <c r="AB8" t="n">
         <v>5.11</v>
@@ -3881,7 +3881,7 @@
         <v>19.11</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE8" t="n">
         <v>2.22</v>
@@ -4175,10 +4175,10 @@
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.56</v>
+        <v>11.53</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.06</v>
+        <v>7.03</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.5</v>
@@ -4187,7 +4187,7 @@
         <v>17.47</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC8" t="n">
         <v>2.44</v>
@@ -4242,13 +4242,13 @@
         <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>8.81</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="Q9" t="n">
         <v>10.56</v>
       </c>
       <c r="R9" t="n">
-        <v>7.19</v>
+        <v>7.25</v>
       </c>
       <c r="S9" t="n">
         <v>0.8100000000000001</v>
@@ -4272,10 +4272,10 @@
         <v>0.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.25</v>
+        <v>13.19</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.44</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AB9" t="n">
         <v>4.81</v>
@@ -4554,13 +4554,13 @@
         <v>2.18</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.06</v>
+        <v>10.1</v>
       </c>
       <c r="DQ9" t="n">
         <v>10.78</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.470000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DS9" t="n">
         <v>0.09</v>
@@ -4578,10 +4578,10 @@
         <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.75</v>
+        <v>10.72</v>
       </c>
       <c r="DY9" t="n">
-        <v>7</v>
+        <v>6.97</v>
       </c>
       <c r="DZ9" t="n">
         <v>3.75</v>
@@ -4831,13 +4831,13 @@
         <v>2.45</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CA10" t="n">
         <v>3.07</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CC10" t="n">
         <v>3.34</v>
@@ -4915,13 +4915,13 @@
         <v>1.59</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="DD10" t="n">
-        <v>5.31</v>
+        <v>5.29</v>
       </c>
       <c r="DE10" t="n">
         <v>0.06</v>
@@ -5481,19 +5481,19 @@
         <v>0.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.88</v>
+        <v>13.94</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.619999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="AB12" t="n">
         <v>5.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.88</v>
+        <v>17.94</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="n">
         <v>2.62</v>
@@ -5787,16 +5787,16 @@
         <v>0.24</v>
       </c>
       <c r="DX12" t="n">
-        <v>12</v>
+        <v>12.03</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.75</v>
+        <v>7.79</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.24</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.21</v>
+        <v>18.24</v>
       </c>
       <c r="EB12" t="n">
         <v>1.45</v>
@@ -6046,13 +6046,13 @@
         <v>3.04</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CC13" t="n">
         <v>4.65</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.72</v>
+        <v>5.71</v>
       </c>
       <c r="CE13" t="n">
         <v>1.58</v>
@@ -6109,13 +6109,13 @@
         <v>1.57</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.19</v>
@@ -6127,10 +6127,10 @@
         <v>1.63</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="DD13" t="n">
-        <v>6.21</v>
+        <v>6.24</v>
       </c>
       <c r="DE13" t="n">
         <v>0.06</v>
@@ -6287,19 +6287,19 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.75</v>
+        <v>11.94</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.81</v>
+        <v>8.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="n">
         <v>23.06</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -6593,19 +6593,19 @@
         <v>0.06</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.78</v>
+        <v>10.88</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.68</v>
+        <v>7.75</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="EA14" t="n">
         <v>21.94</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="EC14" t="n">
         <v>2.9</v>
@@ -6852,13 +6852,13 @@
         <v>2.81</v>
       </c>
       <c r="CB15" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CC15" t="n">
         <v>3.54</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CE15" t="n">
         <v>1.67</v>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="CS15" t="inlineStr"/>
       <c r="CT15" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CU15" t="inlineStr"/>
       <c r="CV15" t="n">
@@ -6929,7 +6929,7 @@
         <v>1.8</v>
       </c>
       <c r="DC15" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="DD15" t="n">
         <v>6.86</v>
@@ -7569,10 +7569,10 @@
         <v>0.06</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.65</v>
+        <v>7.71</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
       <c r="BC17" t="n">
         <v>3.12</v>
@@ -7581,7 +7581,7 @@
         <v>19.06</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BF17" t="n">
         <v>2.88</v>
@@ -7650,13 +7650,13 @@
         <v>2.99</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CC17" t="n">
         <v>4.11</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="CE17" t="n">
         <v>1.59</v>
@@ -7713,7 +7713,7 @@
         <v>1.65</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CX17" t="n">
         <v>1.84</v>
@@ -7731,10 +7731,10 @@
         <v>1.59</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="DD17" t="n">
-        <v>5.91</v>
+        <v>5.9</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
@@ -7794,10 +7794,10 @@
         <v>0.24</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.82</v>
+        <v>9.85</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.15</v>
+        <v>6.19</v>
       </c>
       <c r="DZ17" t="n">
         <v>3.67</v>
@@ -9248,13 +9248,13 @@
         <v>2.96</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="CA21" t="n">
         <v>2.85</v>
       </c>
       <c r="CB21" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CC21" t="n">
         <v>4.11</v>
@@ -9316,7 +9316,7 @@
         <v>2.7</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CY21" t="n">
         <v>2.4</v>
@@ -9328,13 +9328,13 @@
         <v>1.56</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DC21" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="DD21" t="n">
-        <v>6.5</v>
+        <v>6.52</v>
       </c>
       <c r="DE21" t="n">
         <v>0.05</v>
@@ -12867,7 +12867,7 @@
         <v>3.53</v>
       </c>
       <c r="CD30" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="CE30" t="n">
         <v>1.58</v>
@@ -12909,31 +12909,31 @@
         <v>5.45</v>
       </c>
       <c r="CR30" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CS30" t="n">
         <v>3.24</v>
       </c>
       <c r="CT30" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CU30" t="n">
         <v>1.33</v>
       </c>
       <c r="CV30" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CW30" t="n">
         <v>2.34</v>
       </c>
       <c r="CX30" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CY30" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CZ30" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DA30" t="n">
         <v>1.64</v>
@@ -12942,7 +12942,7 @@
         <v>1.58</v>
       </c>
       <c r="DC30" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DD30" t="n">
         <v>5.78</v>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
         <v>0.11</v>
@@ -1875,49 +1875,49 @@
         <v>0.12</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>99.44</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>53.19</v>
+        <v>53</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.06</v>
+        <v>11.41</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.31</v>
+        <v>12.59</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.12</v>
+        <v>6.94</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>60.94</v>
+        <v>61.06</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.69</v>
+        <v>11.65</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.38</v>
+        <v>18.94</v>
       </c>
       <c r="BE3" t="n">
         <v>1.43</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="BG3" t="n">
         <v>2.06</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.56</v>
+        <v>8.49</v>
       </c>
       <c r="BI3" t="n">
         <v>2.06</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.35</v>
+        <v>4.26</v>
       </c>
       <c r="BR3" t="n">
-        <v>82.34999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="BS3" t="n">
-        <v>61.76</v>
+        <v>62.86</v>
       </c>
       <c r="BT3" t="n">
-        <v>35.29</v>
+        <v>34.29</v>
       </c>
       <c r="BU3" t="n">
-        <v>17.65</v>
+        <v>17.14</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.82</v>
+        <v>8.57</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>38.24</v>
+        <v>37.14</v>
       </c>
       <c r="BY3" t="n">
         <v>1.8</v>
@@ -2013,22 +2013,22 @@
         <v>1.86</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="CE3" t="n">
         <v>1.58</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CG3" t="n">
         <v>2.31</v>
@@ -2040,13 +2040,13 @@
         <v>1.57</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CK3" t="n">
         <v>1.75</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CM3" t="n">
         <v>2.03</v>
@@ -2061,7 +2061,7 @@
         <v>2.67</v>
       </c>
       <c r="CQ3" t="n">
-        <v>5.25</v>
+        <v>5.27</v>
       </c>
       <c r="CR3" t="n">
         <v>1.63</v>
@@ -2079,7 +2079,7 @@
         <v>1.59</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CX3" t="n">
         <v>1.85</v>
@@ -2088,7 +2088,7 @@
         <v>2.3</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DA3" t="n">
         <v>1.61</v>
@@ -2097,52 +2097,52 @@
         <v>1.61</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="DE3" t="n">
         <v>0.11</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="DH3" t="n">
-        <v>104.91</v>
+        <v>104.43</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="DM3" t="n">
-        <v>59.62</v>
+        <v>59.34</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.41</v>
+        <v>11.11</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.38</v>
+        <v>13.48</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.7</v>
+        <v>6.63</v>
       </c>
       <c r="DS3" t="n">
         <v>0.03</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.65</v>
+        <v>62.66</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.42</v>
+        <v>12.38</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.85</v>
+        <v>7.82</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.48</v>
+        <v>19.26</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="4">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
         <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="G8" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="H8" t="n">
-        <v>100.33</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="K8" t="n">
-        <v>5.83</v>
+        <v>5.74</v>
       </c>
       <c r="L8" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>59.67</v>
+        <v>58.89</v>
       </c>
       <c r="N8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="O8" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="P8" t="n">
-        <v>11</v>
+        <v>10.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.61</v>
+        <v>13.58</v>
       </c>
       <c r="R8" t="n">
-        <v>7.61</v>
+        <v>7.84</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="T8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>57.22</v>
+        <v>56.37</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
+        <v>12.84</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.89</v>
+        <v>7.74</v>
       </c>
       <c r="AB8" t="n">
         <v>5.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.11</v>
+        <v>18.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AF8" t="n">
         <v>0.06</v>
@@ -3968,70 +3968,70 @@
         <v>2.69</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="BH8" t="n">
         <v>9.029999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="BK8" t="n">
         <v>0.29</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.44</v>
+        <v>4.46</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.18000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.47</v>
+        <v>77.14</v>
       </c>
       <c r="BT8" t="n">
-        <v>38.24</v>
+        <v>37.14</v>
       </c>
       <c r="BU8" t="n">
-        <v>14.71</v>
+        <v>14.29</v>
       </c>
       <c r="BV8" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>41.18</v>
+        <v>40</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CC8" t="n">
         <v>2.73</v>
@@ -4040,34 +4040,34 @@
         <v>2.76</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CK8" t="n">
         <v>1.69</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CO8" t="n">
         <v>1.51</v>
@@ -4076,7 +4076,7 @@
         <v>2.58</v>
       </c>
       <c r="CQ8" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="CR8" t="n">
         <v>1.59</v>
@@ -4094,7 +4094,7 @@
         <v>1.62</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CX8" t="n">
         <v>1.78</v>
@@ -4109,88 +4109,88 @@
         <v>1.65</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="DC8" t="n">
         <v>2.73</v>
       </c>
       <c r="DD8" t="n">
-        <v>5.43</v>
+        <v>5.44</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.38</v>
+        <v>96.31</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="DK8" t="n">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="DM8" t="n">
-        <v>56.71</v>
+        <v>56.37</v>
       </c>
       <c r="DN8" t="n">
         <v>1.06</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.18</v>
+        <v>10.97</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.5</v>
+        <v>13.49</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.32</v>
+        <v>7.46</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>56.82</v>
+        <v>56.37</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.53</v>
+        <v>11.49</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.03</v>
+        <v>6.97</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.47</v>
+        <v>17.25</v>
       </c>
       <c r="EB8" t="n">
         <v>1.45</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
         <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="G9" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="H9" t="n">
-        <v>101.69</v>
+        <v>98.47</v>
       </c>
       <c r="I9" t="n">
         <v>-0.06</v>
       </c>
       <c r="J9" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="K9" t="n">
-        <v>5.31</v>
+        <v>5.24</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="M9" t="n">
-        <v>53.88</v>
+        <v>53.24</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="P9" t="n">
-        <v>8.880000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.56</v>
+        <v>10.53</v>
       </c>
       <c r="R9" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="T9" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="U9" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="V9" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.75</v>
+        <v>51.94</v>
       </c>
       <c r="Y9" t="n">
         <v>0.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.19</v>
+        <v>13.24</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.380000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.81</v>
+        <v>4.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.12</v>
+        <v>20.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AF9" t="n">
         <v>0.06</v>
@@ -4371,70 +4371,70 @@
         <v>2.19</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.69</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="BR9" t="n">
-        <v>84.38</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>68.75</v>
+        <v>69.7</v>
       </c>
       <c r="BT9" t="n">
-        <v>40.62</v>
+        <v>42.42</v>
       </c>
       <c r="BU9" t="n">
-        <v>18.75</v>
+        <v>18.18</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.25</v>
+        <v>6.06</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.88</v>
+        <v>48.48</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CC9" t="n">
         <v>3.89</v>
@@ -4443,28 +4443,28 @@
         <v>4.43</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CH9" t="n">
         <v>1.25</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CM9" t="n">
         <v>1.82</v>
@@ -4473,37 +4473,37 @@
         <v>1.5</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.92</v>
+        <v>4.97</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="CS9" t="n">
         <v>3.31</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="CU9" t="n">
         <v>1.32</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CZ9" t="n">
         <v>1.89</v>
@@ -4512,88 +4512,88 @@
         <v>1.55</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="DD9" t="n">
-        <v>5.87</v>
+        <v>5.92</v>
       </c>
       <c r="DE9" t="n">
         <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="DH9" t="n">
-        <v>97.04000000000001</v>
+        <v>95.52</v>
       </c>
       <c r="DI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="DM9" t="n">
-        <v>52.75</v>
+        <v>52.45</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.1</v>
+        <v>10.18</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.78</v>
+        <v>10.76</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.82</v>
+        <v>50.94</v>
       </c>
       <c r="DW9" t="n">
         <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.72</v>
+        <v>10.82</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.97</v>
+        <v>7.09</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.84</v>
+        <v>19.91</v>
       </c>
       <c r="EB9" t="n">
         <v>1.33</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="10">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
         <v>0.12</v>
@@ -5502,136 +5502,136 @@
         <v>0.06</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AI12" t="n">
-        <v>100.24</v>
+        <v>98.33</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.82</v>
+        <v>3.94</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.41</v>
+        <v>3.28</v>
       </c>
       <c r="AM12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>47.56</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>52.22</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BK12" t="n">
         <v>0.35</v>
       </c>
-      <c r="AN12" t="n">
-        <v>48.88</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>53.29</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.33</v>
-      </c>
       <c r="BL12" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="BO12" t="n">
         <v>0.88</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.94</v>
+        <v>94.12</v>
       </c>
       <c r="BS12" t="n">
-        <v>69.7</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>36.36</v>
+        <v>35.29</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.18</v>
+        <v>17.65</v>
       </c>
       <c r="BV12" t="n">
-        <v>6.06</v>
+        <v>5.88</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>48.48</v>
+        <v>47.06</v>
       </c>
       <c r="BY12" t="n">
         <v>2.03</v>
@@ -5643,13 +5643,13 @@
         <v>3.1</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="CE12" t="n">
         <v>1.55</v>
@@ -5658,10 +5658,10 @@
         <v>3.56</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CI12" t="n">
         <v>1.63</v>
@@ -5691,13 +5691,13 @@
         <v>5.17</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CS12" t="n">
         <v>3.4</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CU12" t="n">
         <v>1.32</v>
@@ -5706,13 +5706,13 @@
         <v>1.63</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CX12" t="n">
         <v>1.76</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.09</v>
@@ -5724,52 +5724,52 @@
         <v>1.6</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DD12" t="n">
-        <v>5.88</v>
+        <v>5.93</v>
       </c>
       <c r="DE12" t="n">
         <v>0.09</v>
       </c>
       <c r="DF12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>102.26</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>53</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DO12" t="n">
         <v>2.12</v>
       </c>
-      <c r="DG12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DH12" t="n">
-        <v>103.37</v>
-      </c>
-      <c r="DI12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DJ12" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="DK12" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="DL12" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="DM12" t="n">
-        <v>53.84</v>
-      </c>
-      <c r="DN12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="DO12" t="n">
-        <v>2.15</v>
-      </c>
       <c r="DP12" t="n">
-        <v>13.55</v>
+        <v>13.85</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.12</v>
+        <v>12.06</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.91</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="DS12" t="n">
         <v>0.06</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.18</v>
+        <v>55.53</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.03</v>
+        <v>11.91</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.79</v>
+        <v>7.71</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.24</v>
+        <v>18.03</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="EC12" t="n">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="13">
@@ -10225,94 +10225,94 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
         <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="F24" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="G24" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="H24" t="n">
-        <v>95.56</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="J24" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="K24" t="n">
-        <v>5.89</v>
+        <v>5.74</v>
       </c>
       <c r="L24" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="M24" t="n">
-        <v>56.5</v>
+        <v>57.58</v>
       </c>
       <c r="N24" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="O24" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="P24" t="n">
-        <v>10.5</v>
+        <v>10.47</v>
       </c>
       <c r="Q24" t="n">
-        <v>14.39</v>
+        <v>14.89</v>
       </c>
       <c r="R24" t="n">
-        <v>7</v>
+        <v>6.89</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="T24" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="U24" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="V24" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>56.72</v>
+        <v>57.21</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>12.17</v>
+        <v>12.37</v>
       </c>
       <c r="AA24" t="n">
-        <v>7.17</v>
+        <v>7.47</v>
       </c>
       <c r="AB24" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="AC24" t="n">
-        <v>22.06</v>
+        <v>22.26</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AF24" t="n">
         <v>0.12</v>
@@ -10396,49 +10396,49 @@
         <v>3</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="BH24" t="n">
-        <v>9.529999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="BL24" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="BM24" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="BN24" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="BO24" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP24" t="n">
-        <v>4.68</v>
+        <v>4.6</v>
       </c>
       <c r="BQ24" t="n">
-        <v>4.85</v>
+        <v>4.77</v>
       </c>
       <c r="BR24" t="n">
-        <v>79.41</v>
+        <v>80</v>
       </c>
       <c r="BS24" t="n">
-        <v>50</v>
+        <v>48.57</v>
       </c>
       <c r="BT24" t="n">
-        <v>35.29</v>
+        <v>34.29</v>
       </c>
       <c r="BU24" t="n">
-        <v>8.82</v>
+        <v>8.57</v>
       </c>
       <c r="BV24" t="n">
         <v>0</v>
@@ -10447,19 +10447,19 @@
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>38.24</v>
+        <v>37.14</v>
       </c>
       <c r="BY24" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BZ24" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="CA24" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CB24" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CC24" t="n">
         <v>3.5</v>
@@ -10471,7 +10471,7 @@
         <v>1.63</v>
       </c>
       <c r="CF24" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CG24" t="n">
         <v>2.23</v>
@@ -10483,7 +10483,7 @@
         <v>1.54</v>
       </c>
       <c r="CJ24" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CK24" t="n">
         <v>1.68</v>
@@ -10501,17 +10501,17 @@
         <v>1.59</v>
       </c>
       <c r="CP24" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CQ24" t="n">
-        <v>5.83</v>
+        <v>5.81</v>
       </c>
       <c r="CR24" t="n">
         <v>1.63</v>
       </c>
       <c r="CS24" t="inlineStr"/>
       <c r="CT24" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CU24" t="inlineStr"/>
       <c r="CV24" t="n">
@@ -10521,7 +10521,7 @@
         <v>2.52</v>
       </c>
       <c r="CX24" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY24" t="n">
         <v>2.18</v>
@@ -10533,55 +10533,55 @@
         <v>1.68</v>
       </c>
       <c r="DB24" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DC24" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="DD24" t="n">
-        <v>6.19</v>
+        <v>6.22</v>
       </c>
       <c r="DE24" t="n">
         <v>0.17</v>
       </c>
       <c r="DF24" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="DG24" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DH24" t="n">
-        <v>86.83</v>
+        <v>87.97</v>
       </c>
       <c r="DI24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ24" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="DK24" t="n">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="DL24" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM24" t="n">
-        <v>52.94</v>
+        <v>53.63</v>
       </c>
       <c r="DN24" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="DO24" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="DP24" t="n">
-        <v>11.09</v>
+        <v>11.06</v>
       </c>
       <c r="DQ24" t="n">
-        <v>13.09</v>
+        <v>13.4</v>
       </c>
       <c r="DR24" t="n">
-        <v>8.529999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DS24" t="n">
         <v>0.23</v>
@@ -10593,28 +10593,28 @@
         <v>0</v>
       </c>
       <c r="DV24" t="n">
-        <v>53.79</v>
+        <v>54.14</v>
       </c>
       <c r="DW24" t="n">
         <v>0</v>
       </c>
       <c r="DX24" t="n">
-        <v>10.33</v>
+        <v>10.49</v>
       </c>
       <c r="DY24" t="n">
-        <v>6.12</v>
+        <v>6.31</v>
       </c>
       <c r="DZ24" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="EA24" t="n">
-        <v>19.47</v>
+        <v>19.65</v>
       </c>
       <c r="EB24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC24" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="25">
@@ -10624,13 +10624,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25" t="n">
         <v>18</v>
       </c>
       <c r="D25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
         <v>0.17</v>
@@ -10717,136 +10717,136 @@
         <v>0.06</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AH25" t="n">
         <v>2.06</v>
       </c>
       <c r="AI25" t="n">
-        <v>97.23999999999999</v>
+        <v>93.89</v>
       </c>
       <c r="AJ25" t="n">
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AL25" t="n">
-        <v>4.18</v>
+        <v>4.06</v>
       </c>
       <c r="AM25" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BL25" t="n">
         <v>0.47</v>
       </c>
-      <c r="AN25" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>13.76</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>13.82</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>46.82</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>22.82</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>0.43</v>
-      </c>
       <c r="BM25" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BN25" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="BO25" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="BP25" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="BR25" t="n">
-        <v>77.14</v>
+        <v>77.78</v>
       </c>
       <c r="BS25" t="n">
-        <v>48.57</v>
+        <v>50</v>
       </c>
       <c r="BT25" t="n">
-        <v>22.86</v>
+        <v>25</v>
       </c>
       <c r="BU25" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BV25" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BW25" t="n">
         <v>0</v>
       </c>
       <c r="BX25" t="n">
-        <v>37.14</v>
+        <v>38.89</v>
       </c>
       <c r="BY25" t="n">
         <v>2.46</v>
@@ -10858,25 +10858,25 @@
         <v>2.8</v>
       </c>
       <c r="CB25" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CC25" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CD25" t="n">
-        <v>4.74</v>
+        <v>4.55</v>
       </c>
       <c r="CE25" t="n">
         <v>1.72</v>
       </c>
       <c r="CF25" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="CG25" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CH25" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CI25" t="n">
         <v>1.47</v>
@@ -10903,27 +10903,27 @@
         <v>3.32</v>
       </c>
       <c r="CQ25" t="n">
-        <v>6.95</v>
+        <v>6.94</v>
       </c>
       <c r="CR25" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CS25" t="inlineStr"/>
       <c r="CT25" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CU25" t="inlineStr"/>
       <c r="CV25" t="n">
         <v>1.45</v>
       </c>
       <c r="CW25" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CX25" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CY25" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CZ25" t="n">
         <v>1.9</v>
@@ -10932,88 +10932,88 @@
         <v>1.57</v>
       </c>
       <c r="DB25" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DC25" t="n">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="DD25" t="n">
-        <v>6.86</v>
+        <v>6.84</v>
       </c>
       <c r="DE25" t="n">
         <v>0.12</v>
       </c>
       <c r="DF25" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="DG25" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DH25" t="n">
-        <v>95.37</v>
+        <v>93.75</v>
       </c>
       <c r="DI25" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ25" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="DK25" t="n">
-        <v>4.31</v>
+        <v>4.25</v>
       </c>
       <c r="DL25" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DM25" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="DN25" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="DO25" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DP25" t="n">
-        <v>12.77</v>
+        <v>12.72</v>
       </c>
       <c r="DQ25" t="n">
-        <v>14.77</v>
+        <v>14.73</v>
       </c>
       <c r="DR25" t="n">
-        <v>7.63</v>
+        <v>7.72</v>
       </c>
       <c r="DS25" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT25" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU25" t="n">
         <v>0</v>
       </c>
       <c r="DV25" t="n">
-        <v>47.85</v>
+        <v>47.78</v>
       </c>
       <c r="DW25" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="DX25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="DY25" t="n">
-        <v>6.54</v>
+        <v>6.44</v>
       </c>
       <c r="DZ25" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="EA25" t="n">
-        <v>21.08</v>
+        <v>20.97</v>
       </c>
       <c r="EB25" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC25" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="26">
@@ -11825,13 +11825,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C28" t="n">
         <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E28" t="n">
         <v>0.06</v>
@@ -11921,46 +11921,46 @@
         <v>2.12</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AI28" t="n">
-        <v>87.56</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AK28" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="AL28" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AN28" t="n">
-        <v>44.19</v>
+        <v>45.24</v>
       </c>
       <c r="AO28" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12.69</v>
+        <v>12.24</v>
       </c>
       <c r="AR28" t="n">
-        <v>9.619999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.75</v>
+        <v>7.82</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AV28" t="n">
         <v>0</v>
@@ -11972,82 +11972,82 @@
         <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>53.69</v>
+        <v>54</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BA28" t="n">
-        <v>12.56</v>
+        <v>12.76</v>
       </c>
       <c r="BB28" t="n">
-        <v>8</v>
+        <v>8.24</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="BD28" t="n">
-        <v>16.56</v>
+        <v>16.76</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BF28" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BH28" t="n">
         <v>8.880000000000001</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="BK28" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="BL28" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="BM28" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN28" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BO28" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BP28" t="n">
         <v>4.09</v>
       </c>
       <c r="BQ28" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="BR28" t="n">
-        <v>71.88</v>
+        <v>72.73</v>
       </c>
       <c r="BS28" t="n">
-        <v>43.75</v>
+        <v>45.45</v>
       </c>
       <c r="BT28" t="n">
-        <v>25</v>
+        <v>24.24</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="BV28" t="n">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="BW28" t="n">
         <v>0</v>
       </c>
       <c r="BX28" t="n">
-        <v>34.38</v>
+        <v>33.33</v>
       </c>
       <c r="BY28" t="n">
         <v>2.03</v>
@@ -12056,25 +12056,25 @@
         <v>2.11</v>
       </c>
       <c r="CA28" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CB28" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CC28" t="n">
-        <v>3.03</v>
+        <v>3.24</v>
       </c>
       <c r="CD28" t="n">
-        <v>3.66</v>
+        <v>4.02</v>
       </c>
       <c r="CE28" t="n">
         <v>1.56</v>
       </c>
       <c r="CF28" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CG28" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CH28" t="n">
         <v>1.26</v>
@@ -12083,13 +12083,13 @@
         <v>1.61</v>
       </c>
       <c r="CJ28" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CK28" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CL28" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CM28" t="n">
         <v>2.05</v>
@@ -12104,10 +12104,10 @@
         <v>2.59</v>
       </c>
       <c r="CQ28" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="CR28" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CS28" t="inlineStr"/>
       <c r="CT28" t="n">
@@ -12115,10 +12115,10 @@
       </c>
       <c r="CU28" t="inlineStr"/>
       <c r="CV28" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CW28" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CX28" t="n">
         <v>1.71</v>
@@ -12133,55 +12133,55 @@
         <v>1.69</v>
       </c>
       <c r="DB28" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DC28" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="DD28" t="n">
-        <v>6.05</v>
+        <v>6.02</v>
       </c>
       <c r="DE28" t="n">
         <v>0.06</v>
       </c>
       <c r="DF28" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DG28" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="DH28" t="n">
-        <v>92.25</v>
+        <v>91.48</v>
       </c>
       <c r="DI28" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ28" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="DK28" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="DL28" t="n">
         <v>0.34</v>
       </c>
       <c r="DM28" t="n">
-        <v>48.28</v>
+        <v>48.7</v>
       </c>
       <c r="DN28" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="DO28" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="DP28" t="n">
-        <v>12</v>
+        <v>11.79</v>
       </c>
       <c r="DQ28" t="n">
-        <v>10.9</v>
+        <v>10.88</v>
       </c>
       <c r="DR28" t="n">
-        <v>7.18</v>
+        <v>7.24</v>
       </c>
       <c r="DS28" t="n">
         <v>0</v>
@@ -12193,28 +12193,28 @@
         <v>0</v>
       </c>
       <c r="DV28" t="n">
-        <v>56.16</v>
+        <v>56.24</v>
       </c>
       <c r="DW28" t="n">
         <v>0.18</v>
       </c>
       <c r="DX28" t="n">
-        <v>13.56</v>
+        <v>13.63</v>
       </c>
       <c r="DY28" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="DZ28" t="n">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="EA28" t="n">
-        <v>16.66</v>
+        <v>16.76</v>
       </c>
       <c r="EB28" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="EC28" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="29">
@@ -13030,10 +13030,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D31" t="n">
         <v>16</v>
@@ -13042,49 +13042,49 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>3.31</v>
+        <v>3.12</v>
       </c>
       <c r="H31" t="n">
-        <v>105.56</v>
+        <v>103.71</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J31" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="K31" t="n">
-        <v>6.06</v>
+        <v>5.76</v>
       </c>
       <c r="L31" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="M31" t="n">
-        <v>65.44</v>
+        <v>63.59</v>
       </c>
       <c r="N31" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="O31" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P31" t="n">
-        <v>11.31</v>
+        <v>11.29</v>
       </c>
       <c r="Q31" t="n">
-        <v>14.88</v>
+        <v>14.41</v>
       </c>
       <c r="R31" t="n">
-        <v>7.44</v>
+        <v>7.29</v>
       </c>
       <c r="S31" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="T31" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="U31" t="n">
         <v>0.12</v>
@@ -13096,28 +13096,28 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>59.25</v>
+        <v>57.94</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>11.06</v>
+        <v>10.88</v>
       </c>
       <c r="AA31" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.81</v>
+        <v>3.88</v>
       </c>
       <c r="AC31" t="n">
-        <v>21.19</v>
+        <v>21.41</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="AF31" t="n">
         <v>0.12</v>
@@ -13204,61 +13204,61 @@
         <v>1.88</v>
       </c>
       <c r="BH31" t="n">
-        <v>8.94</v>
+        <v>8.85</v>
       </c>
       <c r="BI31" t="n">
         <v>1.88</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="BK31" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL31" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BM31" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="BN31" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BO31" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP31" t="n">
-        <v>4.03</v>
+        <v>4.06</v>
       </c>
       <c r="BQ31" t="n">
-        <v>4.91</v>
+        <v>4.79</v>
       </c>
       <c r="BR31" t="n">
-        <v>81.25</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS31" t="n">
-        <v>56.25</v>
+        <v>57.58</v>
       </c>
       <c r="BT31" t="n">
-        <v>37.5</v>
+        <v>36.36</v>
       </c>
       <c r="BU31" t="n">
-        <v>9.380000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="BV31" t="n">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="BW31" t="n">
         <v>0</v>
       </c>
       <c r="BX31" t="n">
-        <v>28.12</v>
+        <v>27.27</v>
       </c>
       <c r="BY31" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="BZ31" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="CA31" t="n">
         <v>2.92</v>
@@ -13294,10 +13294,10 @@
         <v>1.71</v>
       </c>
       <c r="CL31" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CM31" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CN31" t="n">
         <v>1.65</v>
@@ -13309,7 +13309,7 @@
         <v>2.95</v>
       </c>
       <c r="CQ31" t="n">
-        <v>5.92</v>
+        <v>5.93</v>
       </c>
       <c r="CR31" t="n">
         <v>1.72</v>
@@ -13323,7 +13323,7 @@
         <v>1.56</v>
       </c>
       <c r="CW31" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CX31" t="n">
         <v>1.79</v>
@@ -13341,52 +13341,52 @@
         <v>1.74</v>
       </c>
       <c r="DC31" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="DD31" t="n">
-        <v>6.67</v>
+        <v>6.66</v>
       </c>
       <c r="DE31" t="n">
         <v>0.06</v>
       </c>
       <c r="DF31" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="DG31" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="DH31" t="n">
-        <v>97.66</v>
+        <v>96.94</v>
       </c>
       <c r="DI31" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DJ31" t="n">
-        <v>3.16</v>
+        <v>3.24</v>
       </c>
       <c r="DK31" t="n">
-        <v>5.03</v>
+        <v>4.91</v>
       </c>
       <c r="DL31" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="DM31" t="n">
-        <v>54.88</v>
+        <v>54.24</v>
       </c>
       <c r="DN31" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DO31" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="DP31" t="n">
-        <v>13.16</v>
+        <v>13.09</v>
       </c>
       <c r="DQ31" t="n">
-        <v>14.5</v>
+        <v>14.27</v>
       </c>
       <c r="DR31" t="n">
-        <v>8.25</v>
+        <v>8.15</v>
       </c>
       <c r="DS31" t="n">
         <v>0.06</v>
@@ -13398,28 +13398,28 @@
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>54.94</v>
+        <v>54.39</v>
       </c>
       <c r="DW31" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="DX31" t="n">
-        <v>9.31</v>
+        <v>9.27</v>
       </c>
       <c r="DY31" t="n">
-        <v>5.94</v>
+        <v>5.85</v>
       </c>
       <c r="DZ31" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="EA31" t="n">
-        <v>21</v>
+        <v>21.12</v>
       </c>
       <c r="EB31" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC31" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
         <v>0.12</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>86.76000000000001</v>
+        <v>88.39</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.88</v>
+        <v>41.56</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.12</v>
+        <v>12.44</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.65</v>
+        <v>10.89</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.18</v>
+        <v>9.56</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>38.35</v>
+        <v>39</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.41</v>
+        <v>8.44</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.47</v>
+        <v>5.61</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="BD6" t="n">
-        <v>15.12</v>
+        <v>15.67</v>
       </c>
       <c r="BE6" t="n">
         <v>1.04</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.61</v>
+        <v>7.68</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BP6" t="n">
         <v>2.97</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.91</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>72.73</v>
+        <v>70.59</v>
       </c>
       <c r="BT6" t="n">
-        <v>42.42</v>
+        <v>41.18</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.21</v>
+        <v>20.59</v>
       </c>
       <c r="BV6" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="BX6" t="n">
-        <v>57.58</v>
+        <v>55.88</v>
       </c>
       <c r="BY6" t="n">
         <v>3.3</v>
@@ -3222,28 +3222,28 @@
         <v>3.17</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.09</v>
+        <v>5.02</v>
       </c>
       <c r="CD6" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CI6" t="n">
         <v>1.57</v>
@@ -3252,7 +3252,7 @@
         <v>2.29</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CL6" t="n">
         <v>2.35</v>
@@ -3267,10 +3267,10 @@
         <v>1.55</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CQ6" t="n">
-        <v>5.39</v>
+        <v>5.41</v>
       </c>
       <c r="CR6" t="n">
         <v>1.64</v>
@@ -3288,7 +3288,7 @@
         <v>1.58</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CX6" t="n">
         <v>1.9</v>
@@ -3303,55 +3303,55 @@
         <v>1.58</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="DD6" t="n">
-        <v>6.06</v>
+        <v>6.15</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="DH6" t="n">
-        <v>84.20999999999999</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="DK6" t="n">
         <v>2.91</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.18</v>
+        <v>43.47</v>
       </c>
       <c r="DN6" t="n">
         <v>1.06</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.73</v>
+        <v>11.91</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.94</v>
+        <v>12.03</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.85</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DS6" t="n">
         <v>0.15</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>39.82</v>
+        <v>40.12</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>8.67</v>
+        <v>8.68</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.09</v>
+        <v>5.18</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.55</v>
+        <v>16.79</v>
       </c>
       <c r="EB6" t="n">
         <v>1.12</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="7">
@@ -3872,10 +3872,10 @@
         <v>12.84</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.74</v>
+        <v>7.68</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.11</v>
+        <v>5.16</v>
       </c>
       <c r="AC8" t="n">
         <v>18.63</v>
@@ -4178,10 +4178,10 @@
         <v>11.49</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.97</v>
+        <v>6.94</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.52</v>
+        <v>4.54</v>
       </c>
       <c r="EA8" t="n">
         <v>17.25</v>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
         <v>17</v>
@@ -5018,49 +5018,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="G11" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="H11" t="n">
-        <v>93.44</v>
+        <v>95.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J11" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.47</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="M11" t="n">
-        <v>49.75</v>
+        <v>50.65</v>
       </c>
       <c r="N11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>15.44</v>
+        <v>15.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.19</v>
+        <v>11.59</v>
       </c>
       <c r="R11" t="n">
-        <v>8.5</v>
+        <v>7.94</v>
       </c>
       <c r="S11" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="U11" t="n">
         <v>0.06</v>
@@ -5072,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>34.12</v>
+        <v>35.06</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.31</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.12</v>
+        <v>5.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.69</v>
+        <v>18.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5177,70 +5177,70 @@
         <v>3.24</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.48</v>
+        <v>9.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="BN11" t="n">
         <v>1.12</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
       <c r="BR11" t="n">
-        <v>78.79000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="BS11" t="n">
-        <v>48.48</v>
+        <v>47.06</v>
       </c>
       <c r="BT11" t="n">
-        <v>27.27</v>
+        <v>26.47</v>
       </c>
       <c r="BU11" t="n">
-        <v>9.09</v>
+        <v>8.82</v>
       </c>
       <c r="BV11" t="n">
-        <v>6.06</v>
+        <v>5.88</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>30.3</v>
+        <v>29.41</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="CA11" t="n">
         <v>2.93</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CC11" t="n">
         <v>4.3</v>
@@ -5267,22 +5267,22 @@
         <v>2.38</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CM11" t="n">
         <v>2</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CO11" t="n">
         <v>1.67</v>
       </c>
       <c r="CP11" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CQ11" t="n">
         <v>6.33</v>
@@ -5321,52 +5321,52 @@
         <v>1.75</v>
       </c>
       <c r="DC11" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="DD11" t="n">
-        <v>6.72</v>
+        <v>6.78</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="DH11" t="n">
-        <v>87.48</v>
+        <v>88.5</v>
       </c>
       <c r="DI11" t="n">
         <v>0.15</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="DK11" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.79</v>
+        <v>45.38</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DP11" t="n">
-        <v>15.21</v>
+        <v>15.2</v>
       </c>
       <c r="DQ11" t="n">
-        <v>10.27</v>
+        <v>10.5</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.48</v>
+        <v>9.18</v>
       </c>
       <c r="DS11" t="n">
         <v>0.06</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>31.72</v>
+        <v>32.26</v>
       </c>
       <c r="DW11" t="n">
         <v>0.09</v>
       </c>
       <c r="DX11" t="n">
-        <v>7.39</v>
+        <v>7.71</v>
       </c>
       <c r="DY11" t="n">
-        <v>4.39</v>
+        <v>4.68</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.51</v>
+        <v>18.62</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="12">
@@ -5538,7 +5538,7 @@
         <v>11.89</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.83</v>
+        <v>9.94</v>
       </c>
       <c r="AT12" t="n">
         <v>1.39</v>
@@ -5769,7 +5769,7 @@
         <v>12.06</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.029999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="DS12" t="n">
         <v>0.06</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n">
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
         <v>0.06</v>
@@ -5905,49 +5905,49 @@
         <v>0.06</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="AI13" t="n">
-        <v>89.62</v>
+        <v>88.06</v>
       </c>
       <c r="AJ13" t="n">
         <v>0.12</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="AN13" t="n">
-        <v>47</v>
+        <v>45.53</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>12.94</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.25</v>
+        <v>10.18</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.5</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="AV13" t="n">
         <v>0.12</v>
@@ -5959,73 +5959,73 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>43.81</v>
+        <v>43.29</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.06</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.06</v>
+        <v>7.94</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.62</v>
+        <v>5.47</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BD13" t="n">
-        <v>20.19</v>
+        <v>19.76</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.12</v>
+        <v>10.09</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BN13" t="n">
         <v>1.03</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.47</v>
+        <v>4.3</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.66</v>
+        <v>5.45</v>
       </c>
       <c r="BR13" t="n">
-        <v>90.62</v>
+        <v>90.91</v>
       </c>
       <c r="BS13" t="n">
-        <v>53.12</v>
+        <v>54.55</v>
       </c>
       <c r="BT13" t="n">
-        <v>31.25</v>
+        <v>33.33</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>21.88</v>
+        <v>24.24</v>
       </c>
       <c r="BY13" t="n">
         <v>2.7</v>
@@ -6043,25 +6043,25 @@
         <v>3.54</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="CE13" t="n">
         <v>1.58</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CH13" t="n">
         <v>1.24</v>
@@ -6091,7 +6091,7 @@
         <v>2.74</v>
       </c>
       <c r="CQ13" t="n">
-        <v>5.66</v>
+        <v>5.64</v>
       </c>
       <c r="CR13" t="n">
         <v>1.63</v>
@@ -6127,52 +6127,52 @@
         <v>1.63</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="DD13" t="n">
-        <v>6.24</v>
+        <v>6.19</v>
       </c>
       <c r="DE13" t="n">
         <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="DH13" t="n">
-        <v>91.84</v>
+        <v>90.97</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DM13" t="n">
-        <v>52.44</v>
+        <v>51.52</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.12</v>
+        <v>13.09</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.03</v>
+        <v>10.97</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.72</v>
+        <v>7.45</v>
       </c>
       <c r="DS13" t="n">
         <v>0.09</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.94</v>
+        <v>45.6</v>
       </c>
       <c r="DW13" t="n">
         <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.66</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.46</v>
+        <v>6.36</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.28</v>
+        <v>20.06</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="14">
@@ -9419,61 +9419,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
         <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="F22" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="G22" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H22" t="n">
-        <v>103.35</v>
+        <v>103.83</v>
       </c>
       <c r="I22" t="n">
         <v>0.06</v>
       </c>
       <c r="J22" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="K22" t="n">
-        <v>6.41</v>
+        <v>6.39</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>62.24</v>
+        <v>61.78</v>
       </c>
       <c r="N22" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="P22" t="n">
-        <v>12.65</v>
+        <v>12.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.41</v>
+        <v>10.28</v>
       </c>
       <c r="R22" t="n">
-        <v>6.59</v>
+        <v>6.17</v>
       </c>
       <c r="S22" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="T22" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="U22" t="n">
         <v>0.06</v>
@@ -9485,28 +9485,28 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>57.24</v>
+        <v>56.83</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z22" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="AA22" t="n">
-        <v>8.24</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="AC22" t="n">
-        <v>18.41</v>
+        <v>18.78</v>
       </c>
       <c r="AD22" t="n">
         <v>1.49</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -9590,28 +9590,28 @@
         <v>3.06</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="BH22" t="n">
-        <v>9.640000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BO22" t="n">
         <v>0.85</v>
@@ -9620,40 +9620,40 @@
         <v>5.06</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.52</v>
+        <v>4.47</v>
       </c>
       <c r="BR22" t="n">
-        <v>90.91</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="BS22" t="n">
-        <v>54.55</v>
+        <v>55.88</v>
       </c>
       <c r="BT22" t="n">
-        <v>33.33</v>
+        <v>35.29</v>
       </c>
       <c r="BU22" t="n">
-        <v>24.24</v>
+        <v>26.47</v>
       </c>
       <c r="BV22" t="n">
-        <v>15.15</v>
+        <v>17.65</v>
       </c>
       <c r="BW22" t="n">
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>36.36</v>
+        <v>38.24</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="CA22" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CC22" t="n">
         <v>2.7</v>
@@ -9662,7 +9662,7 @@
         <v>3.2</v>
       </c>
       <c r="CE22" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CF22" t="n">
         <v>3.26</v>
@@ -9674,7 +9674,7 @@
         <v>1.31</v>
       </c>
       <c r="CI22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ22" t="n">
         <v>2.02</v>
@@ -9719,7 +9719,7 @@
         <v>2.1</v>
       </c>
       <c r="CX22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY22" t="n">
         <v>2.19</v>
@@ -9734,37 +9734,37 @@
         <v>1.47</v>
       </c>
       <c r="DC22" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DD22" t="n">
-        <v>4.74</v>
+        <v>4.76</v>
       </c>
       <c r="DE22" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DG22" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="DH22" t="n">
-        <v>98.52</v>
+        <v>98.91</v>
       </c>
       <c r="DI22" t="n">
         <v>0.18</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="DK22" t="n">
-        <v>5.3</v>
+        <v>5.32</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DM22" t="n">
-        <v>57.09</v>
+        <v>57</v>
       </c>
       <c r="DN22" t="n">
         <v>1.06</v>
@@ -9773,13 +9773,13 @@
         <v>3.18</v>
       </c>
       <c r="DP22" t="n">
-        <v>13.55</v>
+        <v>13.67</v>
       </c>
       <c r="DQ22" t="n">
-        <v>9.82</v>
+        <v>9.77</v>
       </c>
       <c r="DR22" t="n">
-        <v>8.76</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DS22" t="n">
         <v>0.06</v>
@@ -9791,28 +9791,28 @@
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>54.76</v>
+        <v>54.61</v>
       </c>
       <c r="DW22" t="n">
         <v>0.09</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.21</v>
+        <v>11.23</v>
       </c>
       <c r="DY22" t="n">
-        <v>7.03</v>
+        <v>7.06</v>
       </c>
       <c r="DZ22" t="n">
         <v>4.18</v>
       </c>
       <c r="EA22" t="n">
-        <v>18.73</v>
+        <v>18.91</v>
       </c>
       <c r="EB22" t="n">
         <v>1.42</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="23">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C23" t="n">
         <v>18</v>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
         <v>0.11</v>
@@ -9915,49 +9915,49 @@
         <v>0.12</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="AI23" t="n">
-        <v>96</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="AL23" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AN23" t="n">
-        <v>49.12</v>
+        <v>47.94</v>
       </c>
       <c r="AO23" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12.44</v>
+        <v>12.18</v>
       </c>
       <c r="AR23" t="n">
-        <v>12.44</v>
+        <v>12.76</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.69</v>
+        <v>7.18</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
@@ -9969,82 +9969,82 @@
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>60.69</v>
+        <v>60.06</v>
       </c>
       <c r="AZ23" t="n">
         <v>0.12</v>
       </c>
       <c r="BA23" t="n">
-        <v>11.19</v>
+        <v>11.35</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.31</v>
+        <v>7.35</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="BD23" t="n">
-        <v>20.94</v>
+        <v>20.59</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="BH23" t="n">
-        <v>9</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP23" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="BQ23" t="n">
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
       <c r="BR23" t="n">
-        <v>82.34999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="BS23" t="n">
-        <v>67.65000000000001</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="BT23" t="n">
-        <v>32.35</v>
+        <v>34.29</v>
       </c>
       <c r="BU23" t="n">
-        <v>14.71</v>
+        <v>17.14</v>
       </c>
       <c r="BV23" t="n">
-        <v>5.88</v>
+        <v>8.57</v>
       </c>
       <c r="BW23" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BX23" t="n">
-        <v>38.24</v>
+        <v>40</v>
       </c>
       <c r="BY23" t="n">
         <v>1.52</v>
@@ -10053,16 +10053,16 @@
         <v>1.49</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="CC23" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="CD23" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CE23" t="n">
         <v>1.49</v>
@@ -10077,22 +10077,22 @@
         <v>1.31</v>
       </c>
       <c r="CI23" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CJ23" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CK23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL23" t="n">
         <v>2.24</v>
       </c>
       <c r="CM23" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CO23" t="n">
         <v>1.44</v>
@@ -10107,22 +10107,22 @@
         <v>1.55</v>
       </c>
       <c r="CS23" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="CT23" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CU23" t="n">
         <v>1.35</v>
       </c>
       <c r="CV23" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CX23" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY23" t="n">
         <v>2.19</v>
@@ -10140,49 +10140,49 @@
         <v>2.6</v>
       </c>
       <c r="DD23" t="n">
-        <v>5.12</v>
+        <v>5.13</v>
       </c>
       <c r="DE23" t="n">
         <v>0.11</v>
       </c>
       <c r="DF23" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="DG23" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="DH23" t="n">
-        <v>102.29</v>
+        <v>101.8</v>
       </c>
       <c r="DI23" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ23" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="DK23" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="DL23" t="n">
         <v>0.29</v>
       </c>
       <c r="DM23" t="n">
-        <v>57.68</v>
+        <v>56.86</v>
       </c>
       <c r="DN23" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DO23" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DP23" t="n">
-        <v>13</v>
+        <v>12.86</v>
       </c>
       <c r="DQ23" t="n">
-        <v>13.23</v>
+        <v>13.37</v>
       </c>
       <c r="DR23" t="n">
-        <v>6.85</v>
+        <v>6.63</v>
       </c>
       <c r="DS23" t="n">
         <v>0.06</v>
@@ -10194,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>63.33</v>
+        <v>62.95</v>
       </c>
       <c r="DW23" t="n">
         <v>0.15</v>
@@ -10203,19 +10203,19 @@
         <v>13.94</v>
       </c>
       <c r="DY23" t="n">
-        <v>8.73</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DZ23" t="n">
-        <v>5.21</v>
+        <v>5.23</v>
       </c>
       <c r="EA23" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="EB23" t="n">
         <v>1.66</v>
       </c>
       <c r="EC23" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="24">
@@ -10297,19 +10297,19 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>12.37</v>
+        <v>12.47</v>
       </c>
       <c r="AA24" t="n">
-        <v>7.47</v>
+        <v>7.58</v>
       </c>
       <c r="AB24" t="n">
         <v>4.89</v>
       </c>
       <c r="AC24" t="n">
-        <v>22.26</v>
+        <v>22.32</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE24" t="n">
         <v>2.21</v>
@@ -10599,19 +10599,19 @@
         <v>0</v>
       </c>
       <c r="DX24" t="n">
-        <v>10.49</v>
+        <v>10.54</v>
       </c>
       <c r="DY24" t="n">
-        <v>6.31</v>
+        <v>6.37</v>
       </c>
       <c r="DZ24" t="n">
         <v>4.17</v>
       </c>
       <c r="EA24" t="n">
-        <v>19.65</v>
+        <v>19.69</v>
       </c>
       <c r="EB24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC24" t="n">
         <v>2.57</v>
@@ -12627,10 +12627,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D30" t="n">
         <v>16</v>
@@ -12639,46 +12639,46 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="G30" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="H30" t="n">
-        <v>100.38</v>
+        <v>102.29</v>
       </c>
       <c r="I30" t="n">
         <v>0.06</v>
       </c>
       <c r="J30" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="K30" t="n">
-        <v>6.31</v>
+        <v>6.29</v>
       </c>
       <c r="L30" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="M30" t="n">
-        <v>69.44</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>3.19</v>
+        <v>2.94</v>
       </c>
       <c r="P30" t="n">
-        <v>11.94</v>
+        <v>11.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>12.62</v>
+        <v>12.59</v>
       </c>
       <c r="R30" t="n">
-        <v>7</v>
+        <v>6.53</v>
       </c>
       <c r="S30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="T30" t="n">
         <v>0.9399999999999999</v>
@@ -12693,28 +12693,28 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>54.12</v>
+        <v>54.76</v>
       </c>
       <c r="Y30" t="n">
         <v>0.12</v>
       </c>
       <c r="Z30" t="n">
-        <v>12.69</v>
+        <v>13.24</v>
       </c>
       <c r="AA30" t="n">
-        <v>8.44</v>
+        <v>8.82</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.25</v>
+        <v>4.41</v>
       </c>
       <c r="AC30" t="n">
-        <v>22.12</v>
+        <v>22.47</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AF30" t="n">
         <v>0.06</v>
@@ -12798,70 +12798,70 @@
         <v>2</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="BH30" t="n">
-        <v>9.66</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="BL30" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BM30" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BN30" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BO30" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="BP30" t="n">
-        <v>4.09</v>
+        <v>3.94</v>
       </c>
       <c r="BQ30" t="n">
-        <v>5.56</v>
+        <v>5.36</v>
       </c>
       <c r="BR30" t="n">
-        <v>81.25</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS30" t="n">
-        <v>53.12</v>
+        <v>54.55</v>
       </c>
       <c r="BT30" t="n">
-        <v>31.25</v>
+        <v>33.33</v>
       </c>
       <c r="BU30" t="n">
-        <v>21.88</v>
+        <v>21.21</v>
       </c>
       <c r="BV30" t="n">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="BW30" t="n">
         <v>0</v>
       </c>
       <c r="BX30" t="n">
-        <v>40.62</v>
+        <v>42.42</v>
       </c>
       <c r="BY30" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="BZ30" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="CA30" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CB30" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CC30" t="n">
         <v>3.53</v>
@@ -12876,13 +12876,13 @@
         <v>3.67</v>
       </c>
       <c r="CG30" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CH30" t="n">
         <v>1.24</v>
       </c>
       <c r="CI30" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CJ30" t="n">
         <v>2.25</v>
@@ -12894,7 +12894,7 @@
         <v>2.3</v>
       </c>
       <c r="CM30" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN30" t="n">
         <v>1.6</v>
@@ -12906,7 +12906,7 @@
         <v>2.69</v>
       </c>
       <c r="CQ30" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="CR30" t="n">
         <v>1.61</v>
@@ -12924,70 +12924,70 @@
         <v>1.63</v>
       </c>
       <c r="CW30" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CX30" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CY30" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CZ30" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="DA30" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB30" t="n">
         <v>1.58</v>
       </c>
       <c r="DC30" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="DD30" t="n">
-        <v>5.78</v>
+        <v>5.76</v>
       </c>
       <c r="DE30" t="n">
         <v>0.03</v>
       </c>
       <c r="DF30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DG30" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="DH30" t="n">
-        <v>92.75</v>
+        <v>93.97</v>
       </c>
       <c r="DI30" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ30" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DK30" t="n">
-        <v>5.46</v>
+        <v>5.48</v>
       </c>
       <c r="DL30" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="DM30" t="n">
-        <v>57.38</v>
+        <v>57.42</v>
       </c>
       <c r="DN30" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO30" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="DP30" t="n">
-        <v>11.75</v>
+        <v>11.66</v>
       </c>
       <c r="DQ30" t="n">
-        <v>11.68</v>
+        <v>11.7</v>
       </c>
       <c r="DR30" t="n">
-        <v>8</v>
+        <v>7.73</v>
       </c>
       <c r="DS30" t="n">
         <v>0.03</v>
@@ -12999,25 +12999,25 @@
         <v>0</v>
       </c>
       <c r="DV30" t="n">
-        <v>50.94</v>
+        <v>51.36</v>
       </c>
       <c r="DW30" t="n">
         <v>0.09</v>
       </c>
       <c r="DX30" t="n">
-        <v>12.12</v>
+        <v>12.43</v>
       </c>
       <c r="DY30" t="n">
-        <v>8.220000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="DZ30" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="EA30" t="n">
-        <v>20.22</v>
+        <v>20.45</v>
       </c>
       <c r="EB30" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC30" t="n">
         <v>2.09</v>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
         <v>17</v>
@@ -8230,13 +8230,13 @@
         <v>0.06</v>
       </c>
       <c r="F19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="G19" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="H19" t="n">
-        <v>95.69</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -8245,34 +8245,34 @@
         <v>1.94</v>
       </c>
       <c r="K19" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="L19" t="n">
         <v>0.06</v>
       </c>
       <c r="M19" t="n">
-        <v>48.19</v>
+        <v>48.06</v>
       </c>
       <c r="N19" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="O19" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="P19" t="n">
-        <v>11.12</v>
+        <v>11.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.94</v>
+        <v>12.88</v>
       </c>
       <c r="R19" t="n">
-        <v>7.19</v>
+        <v>6.71</v>
       </c>
       <c r="S19" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="T19" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="U19" t="n">
         <v>0.12</v>
@@ -8284,28 +8284,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>51.31</v>
+        <v>50.71</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.88</v>
+        <v>12.24</v>
       </c>
       <c r="AA19" t="n">
-        <v>6.81</v>
+        <v>7.29</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.06</v>
+        <v>4.94</v>
       </c>
       <c r="AC19" t="n">
-        <v>20.44</v>
+        <v>20.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF19" t="n">
         <v>0.12</v>
@@ -8389,70 +8389,70 @@
         <v>2.18</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.119999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="BK19" t="n">
         <v>0.24</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="BN19" t="n">
         <v>1.03</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.91</v>
+        <v>4.79</v>
       </c>
       <c r="BR19" t="n">
-        <v>81.81999999999999</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>57.58</v>
+        <v>55.88</v>
       </c>
       <c r="BT19" t="n">
-        <v>24.24</v>
+        <v>23.53</v>
       </c>
       <c r="BU19" t="n">
-        <v>6.06</v>
+        <v>5.88</v>
       </c>
       <c r="BV19" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>39.39</v>
+        <v>38.24</v>
       </c>
       <c r="BY19" t="n">
         <v>2.13</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="CA19" t="n">
         <v>2.96</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CC19" t="n">
         <v>3.26</v>
@@ -8473,7 +8473,7 @@
         <v>1.23</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CJ19" t="n">
         <v>2.33</v>
@@ -8482,22 +8482,22 @@
         <v>1.73</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CM19" t="n">
         <v>2.04</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CO19" t="n">
         <v>1.61</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CQ19" t="n">
-        <v>6.07</v>
+        <v>6.06</v>
       </c>
       <c r="CR19" t="n">
         <v>1.72</v>
@@ -8511,40 +8511,40 @@
         <v>1.56</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CX19" t="n">
         <v>1.88</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CZ19" t="n">
         <v>1.93</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DB19" t="n">
         <v>1.73</v>
       </c>
       <c r="DC19" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="DD19" t="n">
-        <v>6.94</v>
+        <v>6.88</v>
       </c>
       <c r="DE19" t="n">
         <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="DH19" t="n">
-        <v>96.12</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
@@ -8553,28 +8553,28 @@
         <v>2.06</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.18</v>
+        <v>4.12</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="DM19" t="n">
-        <v>49</v>
+        <v>48.91</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO19" t="n">
         <v>1.97</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.09</v>
+        <v>11.15</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.36</v>
+        <v>12.35</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.300000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="DS19" t="n">
         <v>0.09</v>
@@ -8586,28 +8586,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.21</v>
+        <v>50.92</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.18</v>
+        <v>11.39</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.91</v>
+        <v>7.14</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.28</v>
+        <v>20.42</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="20">
@@ -12224,13 +12224,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C29" t="n">
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
         <v>0.19</v>
@@ -12314,139 +12314,139 @@
         <v>2.25</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="AI29" t="n">
-        <v>93.23999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="AL29" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="AM29" t="n">
         <v>0.06</v>
       </c>
       <c r="AN29" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AO29" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AQ29" t="n">
-        <v>12.71</v>
+        <v>12.67</v>
       </c>
       <c r="AR29" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.24</v>
+        <v>7.72</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="AU29" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX29" t="n">
         <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>46</v>
+        <v>46.72</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA29" t="n">
-        <v>10.82</v>
+        <v>10.67</v>
       </c>
       <c r="BB29" t="n">
-        <v>7.29</v>
+        <v>7.28</v>
       </c>
       <c r="BC29" t="n">
-        <v>3.53</v>
+        <v>3.39</v>
       </c>
       <c r="BD29" t="n">
-        <v>20.12</v>
+        <v>20.06</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="BH29" t="n">
-        <v>8.359999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="BL29" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="BM29" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN29" t="n">
         <v>1</v>
       </c>
       <c r="BO29" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="BP29" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="BQ29" t="n">
-        <v>4.48</v>
+        <v>4.38</v>
       </c>
       <c r="BR29" t="n">
-        <v>84.84999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="BS29" t="n">
-        <v>57.58</v>
+        <v>55.88</v>
       </c>
       <c r="BT29" t="n">
-        <v>30.3</v>
+        <v>29.41</v>
       </c>
       <c r="BU29" t="n">
-        <v>6.06</v>
+        <v>5.88</v>
       </c>
       <c r="BV29" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="BW29" t="n">
         <v>0</v>
       </c>
       <c r="BX29" t="n">
-        <v>39.39</v>
+        <v>38.24</v>
       </c>
       <c r="BY29" t="n">
         <v>2.54</v>
@@ -12461,10 +12461,10 @@
         <v>2.97</v>
       </c>
       <c r="CC29" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="CD29" t="n">
-        <v>4.41</v>
+        <v>4.46</v>
       </c>
       <c r="CE29" t="n">
         <v>1.61</v>
@@ -12500,7 +12500,7 @@
         <v>1.59</v>
       </c>
       <c r="CP29" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CQ29" t="n">
         <v>5.7</v>
@@ -12536,55 +12536,55 @@
         <v>1.53</v>
       </c>
       <c r="DB29" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DC29" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="DD29" t="n">
-        <v>6.6</v>
+        <v>6.57</v>
       </c>
       <c r="DE29" t="n">
         <v>0.15</v>
       </c>
       <c r="DF29" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="DG29" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="DH29" t="n">
-        <v>89.58</v>
+        <v>89.44</v>
       </c>
       <c r="DI29" t="n">
         <v>0.15</v>
       </c>
       <c r="DJ29" t="n">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="DK29" t="n">
-        <v>4.03</v>
+        <v>3.94</v>
       </c>
       <c r="DL29" t="n">
         <v>0.09</v>
       </c>
       <c r="DM29" t="n">
-        <v>48.48</v>
+        <v>47.5</v>
       </c>
       <c r="DN29" t="n">
         <v>1.06</v>
       </c>
       <c r="DO29" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="DP29" t="n">
-        <v>12.79</v>
+        <v>12.77</v>
       </c>
       <c r="DQ29" t="n">
-        <v>12.18</v>
+        <v>12.21</v>
       </c>
       <c r="DR29" t="n">
-        <v>6.88</v>
+        <v>6.65</v>
       </c>
       <c r="DS29" t="n">
         <v>0.09</v>
@@ -12596,28 +12596,28 @@
         <v>0</v>
       </c>
       <c r="DV29" t="n">
-        <v>45.67</v>
+        <v>46.06</v>
       </c>
       <c r="DW29" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX29" t="n">
-        <v>10.39</v>
+        <v>10.33</v>
       </c>
       <c r="DY29" t="n">
-        <v>6.69</v>
+        <v>6.71</v>
       </c>
       <c r="DZ29" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="EA29" t="n">
-        <v>19.43</v>
+        <v>19.42</v>
       </c>
       <c r="EB29" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="EC29" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="30">

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
         <v>0.11</v>
@@ -1872,52 +1872,52 @@
         <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="AI3" t="n">
-        <v>98.76000000000001</v>
+        <v>101.89</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.47</v>
+        <v>5.56</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="AN3" t="n">
-        <v>53</v>
+        <v>54.11</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.41</v>
+        <v>11.17</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.59</v>
+        <v>12.56</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.94</v>
+        <v>6.83</v>
       </c>
       <c r="AT3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>61.06</v>
+        <v>60.17</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.65</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.29</v>
+        <v>7.11</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.94</v>
+        <v>19.44</v>
       </c>
       <c r="BE3" t="n">
         <v>1.43</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.49</v>
+        <v>8.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BO3" t="n">
         <v>0.86</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.23</v>
+        <v>4.08</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.26</v>
+        <v>4.11</v>
       </c>
       <c r="BR3" t="n">
-        <v>82.86</v>
+        <v>83.33</v>
       </c>
       <c r="BS3" t="n">
-        <v>62.86</v>
+        <v>61.11</v>
       </c>
       <c r="BT3" t="n">
-        <v>34.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>17.14</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>37.14</v>
+        <v>36.11</v>
       </c>
       <c r="BY3" t="n">
         <v>1.8</v>
@@ -2016,13 +2016,13 @@
         <v>3.14</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.46</v>
+        <v>2.65</v>
       </c>
       <c r="CE3" t="n">
         <v>1.58</v>
@@ -2046,10 +2046,10 @@
         <v>1.75</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CN3" t="n">
         <v>1.63</v>
@@ -2064,55 +2064,55 @@
         <v>5.27</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CS3" t="n">
         <v>3.37</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CU3" t="n">
         <v>1.32</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CX3" t="n">
         <v>1.85</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB3" t="n">
         <v>1.61</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="DE3" t="n">
         <v>0.11</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="DH3" t="n">
-        <v>104.43</v>
+        <v>105.84</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
@@ -2121,28 +2121,28 @@
         <v>2.31</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.26</v>
+        <v>5.31</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM3" t="n">
-        <v>59.34</v>
+        <v>59.72</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.48</v>
+        <v>13.44</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.63</v>
+        <v>6.58</v>
       </c>
       <c r="DS3" t="n">
         <v>0.03</v>
@@ -2154,22 +2154,22 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.66</v>
+        <v>62.17</v>
       </c>
       <c r="DW3" t="n">
         <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.38</v>
+        <v>12.28</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.82</v>
+        <v>7.72</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.26</v>
+        <v>19.5</v>
       </c>
       <c r="EB3" t="n">
         <v>1.53</v>
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
         <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
-        <v>98.20999999999999</v>
+        <v>97.05</v>
       </c>
       <c r="I8" t="n">
         <v>0.05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5.74</v>
+        <v>5.55</v>
       </c>
       <c r="L8" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="M8" t="n">
-        <v>58.89</v>
+        <v>57.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>10.63</v>
+        <v>10.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.58</v>
+        <v>13.3</v>
       </c>
       <c r="R8" t="n">
-        <v>7.84</v>
+        <v>8.15</v>
       </c>
       <c r="S8" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="T8" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
         <v>0.05</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>56.37</v>
+        <v>56.3</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.84</v>
+        <v>12.35</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.68</v>
+        <v>7.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.63</v>
+        <v>18.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AF8" t="n">
         <v>0.06</v>
@@ -3968,64 +3968,64 @@
         <v>2.69</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="BH8" t="n">
         <v>9.029999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BO8" t="n">
         <v>0.83</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.6</v>
+        <v>4.44</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.46</v>
+        <v>4.31</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.43000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>77.14</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.14</v>
+        <v>36.11</v>
       </c>
       <c r="BU8" t="n">
-        <v>14.29</v>
+        <v>13.89</v>
       </c>
       <c r="BV8" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>40</v>
+        <v>38.89</v>
       </c>
       <c r="BY8" t="n">
         <v>1.83</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CA8" t="n">
         <v>3.11</v>
@@ -4058,7 +4058,7 @@
         <v>2.22</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CL8" t="n">
         <v>2.25</v>
@@ -4097,19 +4097,19 @@
         <v>2.38</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DC8" t="n">
         <v>2.73</v>
@@ -4118,46 +4118,46 @@
         <v>5.44</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="DH8" t="n">
-        <v>96.31</v>
+        <v>95.72</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.97</v>
+        <v>4.89</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DM8" t="n">
-        <v>56.37</v>
+        <v>55.89</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.97</v>
+        <v>10.95</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.49</v>
+        <v>13.34</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.46</v>
+        <v>7.64</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>56.37</v>
+        <v>56.34</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.49</v>
+        <v>11.25</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.94</v>
+        <v>6.78</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.54</v>
+        <v>4.47</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.25</v>
+        <v>17.28</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
         <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G9" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>98.47</v>
+        <v>93.72</v>
       </c>
       <c r="I9" t="n">
         <v>-0.06</v>
       </c>
       <c r="J9" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="K9" t="n">
-        <v>5.24</v>
+        <v>5.33</v>
       </c>
       <c r="L9" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="M9" t="n">
-        <v>53.24</v>
+        <v>50.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="O9" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="P9" t="n">
-        <v>9.119999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.53</v>
+        <v>10.44</v>
       </c>
       <c r="R9" t="n">
         <v>7</v>
       </c>
       <c r="S9" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="T9" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="U9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.94</v>
+        <v>52.28</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.24</v>
+        <v>12.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.529999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.71</v>
+        <v>4.56</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.24</v>
+        <v>20.56</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF9" t="n">
         <v>0.06</v>
@@ -4371,70 +4371,70 @@
         <v>2.19</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.609999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
         <v>0.24</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.27</v>
+        <v>4.35</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BR9" t="n">
-        <v>84.84999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>69.7</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>42.42</v>
+        <v>41.18</v>
       </c>
       <c r="BU9" t="n">
-        <v>18.18</v>
+        <v>17.65</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.06</v>
+        <v>5.88</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="BX9" t="n">
-        <v>48.48</v>
+        <v>47.06</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="CA9" t="n">
         <v>3.08</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CC9" t="n">
         <v>3.89</v>
@@ -4446,7 +4446,7 @@
         <v>1.57</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="CG9" t="n">
         <v>2.33</v>
@@ -4476,10 +4476,10 @@
         <v>1.53</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="CR9" t="n">
         <v>1.64</v>
@@ -4488,7 +4488,7 @@
         <v>3.31</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CU9" t="n">
         <v>1.32</v>
@@ -4503,10 +4503,10 @@
         <v>1.93</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DA9" t="n">
         <v>1.55</v>
@@ -4515,52 +4515,52 @@
         <v>1.63</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DD9" t="n">
-        <v>5.92</v>
+        <v>5.99</v>
       </c>
       <c r="DE9" t="n">
         <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DH9" t="n">
-        <v>95.52</v>
+        <v>93.09</v>
       </c>
       <c r="DI9" t="n">
         <v>-0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.45</v>
+        <v>4.53</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM9" t="n">
-        <v>52.45</v>
+        <v>51.03</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="DP9" t="n">
         <v>10.18</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.76</v>
+        <v>10.7</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.33</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0.12</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.94</v>
+        <v>51.15</v>
       </c>
       <c r="DW9" t="n">
         <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.82</v>
+        <v>10.62</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.09</v>
+        <v>6.94</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.91</v>
+        <v>20.09</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="10">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="n">
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
         <v>0.12</v>
@@ -5499,52 +5499,52 @@
         <v>2.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AI12" t="n">
-        <v>98.33</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.56</v>
+        <v>45.26</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.72</v>
+        <v>14.47</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.89</v>
+        <v>11.79</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.94</v>
+        <v>10.11</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>52.22</v>
+        <v>51.68</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.11</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.83</v>
+        <v>6.74</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.11</v>
+        <v>17.95</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.710000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.15</v>
+        <v>4.23</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.12</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="BS12" t="n">
-        <v>67.65000000000001</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>35.29</v>
+        <v>34.29</v>
       </c>
       <c r="BU12" t="n">
-        <v>17.65</v>
+        <v>17.14</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.88</v>
+        <v>5.71</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>47.06</v>
+        <v>45.71</v>
       </c>
       <c r="BY12" t="n">
         <v>2.03</v>
@@ -5640,16 +5640,16 @@
         <v>2.18</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
       <c r="CE12" t="n">
         <v>1.55</v>
@@ -5676,133 +5676,133 @@
         <v>2.3</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO12" t="n">
         <v>1.5</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CQ12" t="n">
-        <v>5.17</v>
+        <v>5.18</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CS12" t="n">
         <v>3.4</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CU12" t="n">
         <v>1.32</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="DD12" t="n">
-        <v>5.93</v>
+        <v>5.99</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="DH12" t="n">
-        <v>102.26</v>
+        <v>99.66</v>
       </c>
       <c r="DI12" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="DM12" t="n">
-        <v>53</v>
+        <v>51.6</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.85</v>
+        <v>13.74</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.06</v>
+        <v>12</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.09</v>
+        <v>8.23</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>55.53</v>
+        <v>55.14</v>
       </c>
       <c r="DW12" t="n">
         <v>0.26</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.91</v>
+        <v>11.8</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.71</v>
+        <v>7.63</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.03</v>
+        <v>17.95</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="EC12" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -1878,7 +1878,7 @@
         <v>1.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.11</v>
+        <v>2.39</v>
       </c>
       <c r="AI3" t="n">
         <v>101.89</v>
@@ -1890,10 +1890,10 @@
         <v>2.67</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.56</v>
+        <v>5.61</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.28</v>
+        <v>0.39</v>
       </c>
       <c r="AN3" t="n">
         <v>54.11</v>
@@ -1902,7 +1902,7 @@
         <v>0.83</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="AQ3" t="n">
         <v>11.17</v>
@@ -1956,7 +1956,7 @@
         <v>2.03</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.5</v>
+        <v>8.56</v>
       </c>
       <c r="BI3" t="n">
         <v>2.03</v>
@@ -1980,10 +1980,10 @@
         <v>0.86</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.08</v>
+        <v>4.28</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.11</v>
+        <v>4.28</v>
       </c>
       <c r="BR3" t="n">
         <v>83.33</v>
@@ -2109,7 +2109,7 @@
         <v>1.42</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="DH3" t="n">
         <v>105.84</v>
@@ -2121,10 +2121,10 @@
         <v>2.31</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.31</v>
+        <v>5.34</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="DM3" t="n">
         <v>59.72</v>
@@ -2133,7 +2133,7 @@
         <v>0.77</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="DP3" t="n">
         <v>11</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
         <v>18</v>
@@ -3003,49 +3003,49 @@
         <v>0.12</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G6" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="H6" t="n">
-        <v>81.5</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0.12</v>
       </c>
       <c r="J6" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="K6" t="n">
         <v>2.94</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>45.62</v>
+        <v>45.71</v>
       </c>
       <c r="N6" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="P6" t="n">
-        <v>11.31</v>
+        <v>11.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.31</v>
+        <v>13.18</v>
       </c>
       <c r="R6" t="n">
-        <v>9.5</v>
+        <v>9.65</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="U6" t="n">
         <v>0.12</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>41.38</v>
+        <v>42.41</v>
       </c>
       <c r="Y6" t="n">
         <v>0.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.94</v>
+        <v>8.82</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.69</v>
+        <v>4.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.06</v>
+        <v>18.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3165,19 +3165,19 @@
         <v>2.29</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.68</v>
+        <v>7.71</v>
       </c>
       <c r="BI6" t="n">
         <v>2.29</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BM6" t="n">
         <v>0.74</v>
@@ -3189,43 +3189,43 @@
         <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.18000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>70.59</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>41.18</v>
+        <v>40</v>
       </c>
       <c r="BU6" t="n">
-        <v>20.59</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BX6" t="n">
-        <v>55.88</v>
+        <v>54.29</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CC6" t="n">
         <v>5.02</v>
@@ -3237,7 +3237,7 @@
         <v>1.6</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CG6" t="n">
         <v>2.29</v>
@@ -3249,28 +3249,28 @@
         <v>1.57</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CK6" t="n">
         <v>1.75</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CM6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CN6" t="n">
         <v>1.62</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CP6" t="n">
         <v>2.78</v>
       </c>
       <c r="CQ6" t="n">
-        <v>5.41</v>
+        <v>5.45</v>
       </c>
       <c r="CR6" t="n">
         <v>1.64</v>
@@ -3288,10 +3288,10 @@
         <v>1.58</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CY6" t="n">
         <v>2.37</v>
@@ -3315,43 +3315,43 @@
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="DH6" t="n">
-        <v>85.15000000000001</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="DK6" t="n">
         <v>2.91</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.47</v>
+        <v>43.58</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="DP6" t="n">
         <v>11.91</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.03</v>
+        <v>12</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.529999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="DS6" t="n">
         <v>0.15</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>40.12</v>
+        <v>40.66</v>
       </c>
       <c r="DW6" t="n">
         <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>8.68</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.79</v>
+        <v>17.23</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="7">
@@ -3812,7 +3812,7 @@
         <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
         <v>97.05</v>
@@ -3824,10 +3824,10 @@
         <v>2.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M8" t="n">
         <v>57.9</v>
@@ -3836,7 +3836,7 @@
         <v>0.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
         <v>10.6</v>
@@ -3971,7 +3971,7 @@
         <v>2.19</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.029999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="BI8" t="n">
         <v>2.19</v>
@@ -3995,10 +3995,10 @@
         <v>0.83</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.44</v>
+        <v>4.64</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.31</v>
+        <v>4.47</v>
       </c>
       <c r="BR8" t="n">
         <v>91.67</v>
@@ -4124,7 +4124,7 @@
         <v>1.45</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="DH8" t="n">
         <v>95.72</v>
@@ -4136,10 +4136,10 @@
         <v>2.56</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.89</v>
+        <v>4.92</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="DM8" t="n">
         <v>55.89</v>
@@ -4148,7 +4148,7 @@
         <v>1.08</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="DP8" t="n">
         <v>10.95</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
         <v>0.06</v>
@@ -5905,103 +5905,103 @@
         <v>0.06</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AI13" t="n">
-        <v>88.06</v>
+        <v>87.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="AN13" t="n">
-        <v>45.53</v>
+        <v>45.39</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.94</v>
+        <v>12.78</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.18</v>
+        <v>10.33</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.880000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>43.29</v>
+        <v>43.17</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.06</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.94</v>
+        <v>8</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>19.76</v>
+        <v>19.61</v>
       </c>
       <c r="BE13" t="n">
         <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BG13" t="n">
         <v>1.82</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.09</v>
+        <v>10.06</v>
       </c>
       <c r="BI13" t="n">
         <v>1.82</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="BN13" t="n">
         <v>1.03</v>
@@ -6010,22 +6010,22 @@
         <v>0.79</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.45</v>
+        <v>5.26</v>
       </c>
       <c r="BR13" t="n">
-        <v>90.91</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="BS13" t="n">
-        <v>54.55</v>
+        <v>55.88</v>
       </c>
       <c r="BT13" t="n">
-        <v>33.33</v>
+        <v>32.35</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>24.24</v>
+        <v>23.53</v>
       </c>
       <c r="BY13" t="n">
         <v>2.7</v>
@@ -6043,25 +6043,25 @@
         <v>3.54</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.67</v>
+        <v>5.42</v>
       </c>
       <c r="CE13" t="n">
         <v>1.58</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CH13" t="n">
         <v>1.24</v>
@@ -6076,13 +6076,13 @@
         <v>1.63</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO13" t="n">
         <v>1.57</v>
@@ -6091,7 +6091,7 @@
         <v>2.74</v>
       </c>
       <c r="CQ13" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="CR13" t="n">
         <v>1.63</v>
@@ -6109,19 +6109,19 @@
         <v>1.57</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB13" t="n">
         <v>1.63</v>
@@ -6136,43 +6136,43 @@
         <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="DH13" t="n">
-        <v>90.97</v>
+        <v>90.59</v>
       </c>
       <c r="DI13" t="n">
         <v>0.15</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.27</v>
+        <v>4.32</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="DM13" t="n">
-        <v>51.52</v>
+        <v>51.27</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.09</v>
+        <v>13</v>
       </c>
       <c r="DQ13" t="n">
-        <v>10.97</v>
+        <v>11.03</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.45</v>
+        <v>7.47</v>
       </c>
       <c r="DS13" t="n">
         <v>0.09</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.6</v>
+        <v>45.47</v>
       </c>
       <c r="DW13" t="n">
         <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.36</v>
+        <v>6.35</v>
       </c>
       <c r="DZ13" t="n">
         <v>3.18</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.06</v>
+        <v>19.97</v>
       </c>
       <c r="EB13" t="n">
         <v>1.2</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="14">
@@ -9419,94 +9419,94 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
         <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F22" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="H22" t="n">
-        <v>103.83</v>
+        <v>107.68</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="J22" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="K22" t="n">
-        <v>6.39</v>
+        <v>6.53</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="M22" t="n">
-        <v>61.78</v>
+        <v>63.32</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="O22" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="P22" t="n">
-        <v>12.94</v>
+        <v>13.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.28</v>
+        <v>10.53</v>
       </c>
       <c r="R22" t="n">
-        <v>6.17</v>
+        <v>6.47</v>
       </c>
       <c r="S22" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="T22" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="U22" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="V22" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>56.83</v>
+        <v>57.58</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>12.11</v>
+        <v>12.74</v>
       </c>
       <c r="AA22" t="n">
-        <v>8.220000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="AB22" t="n">
         <v>3.89</v>
       </c>
       <c r="AC22" t="n">
-        <v>18.78</v>
+        <v>19.32</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -9590,70 +9590,70 @@
         <v>3.06</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="BH22" t="n">
-        <v>9.59</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="BP22" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.47</v>
+        <v>4.57</v>
       </c>
       <c r="BR22" t="n">
-        <v>91.18000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="BS22" t="n">
-        <v>55.88</v>
+        <v>54.29</v>
       </c>
       <c r="BT22" t="n">
-        <v>35.29</v>
+        <v>34.29</v>
       </c>
       <c r="BU22" t="n">
-        <v>26.47</v>
+        <v>25.71</v>
       </c>
       <c r="BV22" t="n">
-        <v>17.65</v>
+        <v>17.14</v>
       </c>
       <c r="BW22" t="n">
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>38.24</v>
+        <v>37.14</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="BZ22" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="CA22" t="n">
         <v>3.19</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CC22" t="n">
         <v>2.7</v>
@@ -9674,7 +9674,7 @@
         <v>1.31</v>
       </c>
       <c r="CI22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ22" t="n">
         <v>2.02</v>
@@ -9683,10 +9683,10 @@
         <v>1.64</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CM22" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN22" t="n">
         <v>1.72</v>
@@ -9713,16 +9713,16 @@
         <v>1.33</v>
       </c>
       <c r="CV22" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW22" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CX22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CZ22" t="n">
         <v>2.11</v>
@@ -9731,88 +9731,88 @@
         <v>1.67</v>
       </c>
       <c r="DB22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="DC22" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DD22" t="n">
-        <v>4.76</v>
+        <v>4.79</v>
       </c>
       <c r="DE22" t="n">
         <v>0.03</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="DG22" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="DH22" t="n">
-        <v>98.91</v>
+        <v>101.14</v>
       </c>
       <c r="DI22" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="DK22" t="n">
-        <v>5.32</v>
+        <v>5.43</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="DM22" t="n">
-        <v>57</v>
+        <v>57.97</v>
       </c>
       <c r="DN22" t="n">
         <v>1.06</v>
       </c>
       <c r="DO22" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="DP22" t="n">
-        <v>13.67</v>
+        <v>13.75</v>
       </c>
       <c r="DQ22" t="n">
-        <v>9.77</v>
+        <v>9.92</v>
       </c>
       <c r="DR22" t="n">
-        <v>8.470000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>54.61</v>
+        <v>55.08</v>
       </c>
       <c r="DW22" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.23</v>
+        <v>11.6</v>
       </c>
       <c r="DY22" t="n">
-        <v>7.06</v>
+        <v>7.43</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="EA22" t="n">
-        <v>18.91</v>
+        <v>19.2</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="23">
@@ -12224,13 +12224,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C29" t="n">
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29" t="n">
         <v>0.19</v>
@@ -12317,49 +12317,49 @@
         <v>0.11</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="AI29" t="n">
-        <v>92.78</v>
+        <v>92.63</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="AL29" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AN29" t="n">
-        <v>49</v>
+        <v>48.16</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AQ29" t="n">
-        <v>12.67</v>
+        <v>12.79</v>
       </c>
       <c r="AR29" t="n">
-        <v>10.17</v>
+        <v>10.47</v>
       </c>
       <c r="AS29" t="n">
-        <v>7.72</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AT29" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AU29" t="n">
         <v>0.89</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0.9399999999999999</v>
       </c>
       <c r="AV29" t="n">
         <v>0.11</v>
@@ -12371,82 +12371,82 @@
         <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>46.72</v>
+        <v>45.79</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="BA29" t="n">
-        <v>10.67</v>
+        <v>10.84</v>
       </c>
       <c r="BB29" t="n">
-        <v>7.28</v>
+        <v>7.58</v>
       </c>
       <c r="BC29" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="BD29" t="n">
-        <v>20.06</v>
+        <v>20.26</v>
       </c>
       <c r="BE29" t="n">
         <v>1.27</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="BH29" t="n">
-        <v>8.210000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="BK29" t="n">
         <v>0.26</v>
       </c>
       <c r="BL29" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BM29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BN29" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BO29" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="BP29" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="BQ29" t="n">
-        <v>4.38</v>
+        <v>4.49</v>
       </c>
       <c r="BR29" t="n">
-        <v>85.29000000000001</v>
+        <v>82.86</v>
       </c>
       <c r="BS29" t="n">
-        <v>55.88</v>
+        <v>54.29</v>
       </c>
       <c r="BT29" t="n">
-        <v>29.41</v>
+        <v>28.57</v>
       </c>
       <c r="BU29" t="n">
-        <v>5.88</v>
+        <v>5.71</v>
       </c>
       <c r="BV29" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BW29" t="n">
         <v>0</v>
       </c>
       <c r="BX29" t="n">
-        <v>38.24</v>
+        <v>37.14</v>
       </c>
       <c r="BY29" t="n">
         <v>2.54</v>
@@ -12455,25 +12455,25 @@
         <v>2.8</v>
       </c>
       <c r="CA29" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CB29" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CC29" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="CD29" t="n">
-        <v>4.46</v>
+        <v>4.63</v>
       </c>
       <c r="CE29" t="n">
         <v>1.61</v>
       </c>
       <c r="CF29" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CG29" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CH29" t="n">
         <v>1.24</v>
@@ -12500,10 +12500,10 @@
         <v>1.59</v>
       </c>
       <c r="CP29" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CQ29" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="CR29" t="n">
         <v>1.66</v>
@@ -12524,67 +12524,67 @@
         <v>2.48</v>
       </c>
       <c r="CX29" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CY29" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CZ29" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DA29" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DB29" t="n">
         <v>1.68</v>
       </c>
       <c r="DC29" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="DD29" t="n">
-        <v>6.57</v>
+        <v>6.49</v>
       </c>
       <c r="DE29" t="n">
         <v>0.15</v>
       </c>
       <c r="DF29" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="DG29" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="DH29" t="n">
-        <v>89.44</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="DI29" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="DJ29" t="n">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="DK29" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="DL29" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM29" t="n">
-        <v>47.5</v>
+        <v>47.09</v>
       </c>
       <c r="DN29" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="DO29" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DP29" t="n">
-        <v>12.77</v>
+        <v>12.83</v>
       </c>
       <c r="DQ29" t="n">
-        <v>12.21</v>
+        <v>12.31</v>
       </c>
       <c r="DR29" t="n">
-        <v>6.65</v>
+        <v>7.03</v>
       </c>
       <c r="DS29" t="n">
         <v>0.09</v>
@@ -12596,28 +12596,28 @@
         <v>0</v>
       </c>
       <c r="DV29" t="n">
-        <v>46.06</v>
+        <v>45.57</v>
       </c>
       <c r="DW29" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="DX29" t="n">
-        <v>10.33</v>
+        <v>10.43</v>
       </c>
       <c r="DY29" t="n">
-        <v>6.71</v>
+        <v>6.89</v>
       </c>
       <c r="DZ29" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="EA29" t="n">
-        <v>19.42</v>
+        <v>19.54</v>
       </c>
       <c r="EB29" t="n">
         <v>1.25</v>
       </c>
       <c r="EC29" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="30">

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="H8" t="n">
-        <v>97.05</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>0.05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>5.52</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>57.9</v>
+        <v>58</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>10.6</v>
+        <v>10.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.3</v>
+        <v>13.57</v>
       </c>
       <c r="R8" t="n">
-        <v>8.15</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="T8" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="U8" t="n">
         <v>0.05</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>56.3</v>
+        <v>56.05</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.35</v>
+        <v>12.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.35</v>
+        <v>7.24</v>
       </c>
       <c r="AB8" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.6</v>
+        <v>18.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AF8" t="n">
         <v>0.06</v>
@@ -3968,67 +3968,67 @@
         <v>2.69</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.08</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.64</v>
+        <v>4.51</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>72.97</v>
       </c>
       <c r="BT8" t="n">
-        <v>36.11</v>
+        <v>35.14</v>
       </c>
       <c r="BU8" t="n">
-        <v>13.89</v>
+        <v>13.51</v>
       </c>
       <c r="BV8" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>38.89</v>
+        <v>37.84</v>
       </c>
       <c r="BY8" t="n">
         <v>1.83</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CB8" t="n">
         <v>3.26</v>
@@ -4040,13 +4040,13 @@
         <v>2.76</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CF8" t="n">
         <v>3.49</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CH8" t="n">
         <v>1.26</v>
@@ -4073,10 +4073,10 @@
         <v>1.51</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.99</v>
+        <v>4.98</v>
       </c>
       <c r="CR8" t="n">
         <v>1.59</v>
@@ -4091,19 +4091,19 @@
         <v>1.37</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DA8" t="n">
         <v>1.64</v>
@@ -4112,52 +4112,52 @@
         <v>1.55</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="DD8" t="n">
-        <v>5.44</v>
+        <v>5.4</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="DH8" t="n">
-        <v>95.72</v>
+        <v>95.67</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.92</v>
+        <v>4.89</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="DM8" t="n">
-        <v>55.89</v>
+        <v>56</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.95</v>
+        <v>10.84</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.34</v>
+        <v>13.49</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.64</v>
+        <v>7.65</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>56.34</v>
+        <v>56.19</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.25</v>
+        <v>11.14</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.78</v>
+        <v>6.73</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.47</v>
+        <v>4.41</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.28</v>
+        <v>17.32</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="9">
@@ -9419,13 +9419,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C22" t="n">
         <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
         <v>0.05</v>
@@ -9512,49 +9512,49 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AI22" t="n">
-        <v>93.38</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AK22" t="n">
-        <v>3.19</v>
+        <v>3.35</v>
       </c>
       <c r="AL22" t="n">
-        <v>4.12</v>
+        <v>3.88</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AN22" t="n">
-        <v>51.62</v>
+        <v>50.88</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14.5</v>
+        <v>14.76</v>
       </c>
       <c r="AR22" t="n">
-        <v>9.19</v>
+        <v>9.06</v>
       </c>
       <c r="AS22" t="n">
-        <v>11.06</v>
+        <v>10.94</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AV22" t="n">
         <v>0.06</v>
@@ -9566,82 +9566,82 @@
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>52.12</v>
+        <v>51.94</v>
       </c>
       <c r="AZ22" t="n">
         <v>0.06</v>
       </c>
       <c r="BA22" t="n">
-        <v>10.25</v>
+        <v>10.12</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.75</v>
+        <v>5.76</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="BD22" t="n">
-        <v>19.06</v>
+        <v>18.71</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.06</v>
+        <v>3.24</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BH22" t="n">
-        <v>9.630000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP22" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
       <c r="BR22" t="n">
-        <v>88.56999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS22" t="n">
-        <v>54.29</v>
+        <v>52.78</v>
       </c>
       <c r="BT22" t="n">
-        <v>34.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU22" t="n">
-        <v>25.71</v>
+        <v>25</v>
       </c>
       <c r="BV22" t="n">
-        <v>17.14</v>
+        <v>16.67</v>
       </c>
       <c r="BW22" t="n">
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>37.14</v>
+        <v>36.11</v>
       </c>
       <c r="BY22" t="n">
         <v>1.95</v>
@@ -9650,19 +9650,19 @@
         <v>2.01</v>
       </c>
       <c r="CA22" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CB22" t="n">
         <v>3.25</v>
       </c>
       <c r="CC22" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="CD22" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="CE22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CF22" t="n">
         <v>3.26</v>
@@ -9677,13 +9677,13 @@
         <v>1.75</v>
       </c>
       <c r="CJ22" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK22" t="n">
         <v>1.64</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM22" t="n">
         <v>2.13</v>
@@ -9695,10 +9695,10 @@
         <v>1.42</v>
       </c>
       <c r="CP22" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CQ22" t="n">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="CR22" t="n">
         <v>1.52</v>
@@ -9713,16 +9713,16 @@
         <v>1.33</v>
       </c>
       <c r="CV22" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CW22" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CX22" t="n">
         <v>1.73</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CZ22" t="n">
         <v>2.11</v>
@@ -9743,43 +9743,43 @@
         <v>0.03</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DG22" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="DH22" t="n">
         <v>101.14</v>
       </c>
       <c r="DI22" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="DK22" t="n">
-        <v>5.43</v>
+        <v>5.28</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM22" t="n">
-        <v>57.97</v>
+        <v>57.45</v>
       </c>
       <c r="DN22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DO22" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="DP22" t="n">
-        <v>13.75</v>
+        <v>13.89</v>
       </c>
       <c r="DQ22" t="n">
-        <v>9.92</v>
+        <v>9.84</v>
       </c>
       <c r="DR22" t="n">
-        <v>8.57</v>
+        <v>8.58</v>
       </c>
       <c r="DS22" t="n">
         <v>0.05</v>
@@ -9791,28 +9791,28 @@
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>55.08</v>
+        <v>54.92</v>
       </c>
       <c r="DW22" t="n">
         <v>0.14</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="DY22" t="n">
-        <v>7.43</v>
+        <v>7.39</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
       <c r="EA22" t="n">
-        <v>19.2</v>
+        <v>19.03</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="23">

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" t="n">
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
         <v>0.12</v>
@@ -5502,49 +5502,49 @@
         <v>0.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>93.73999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.26</v>
+        <v>45.95</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.47</v>
+        <v>14.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.79</v>
+        <v>11.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>51.68</v>
+        <v>51.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>9.85</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.74</v>
+        <v>6.55</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="BD12" t="n">
-        <v>17.95</v>
+        <v>18.15</v>
       </c>
       <c r="BE12" t="n">
         <v>1.19</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.77</v>
+        <v>8.69</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
         <v>1.31</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.29000000000001</v>
+        <v>94.44</v>
       </c>
       <c r="BS12" t="n">
-        <v>65.70999999999999</v>
+        <v>63.89</v>
       </c>
       <c r="BT12" t="n">
-        <v>34.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>17.14</v>
+        <v>16.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>45.71</v>
+        <v>44.44</v>
       </c>
       <c r="BY12" t="n">
         <v>2.03</v>
@@ -5640,25 +5640,25 @@
         <v>2.18</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="CE12" t="n">
         <v>1.55</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CH12" t="n">
         <v>1.26</v>
@@ -5667,13 +5667,13 @@
         <v>1.63</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CK12" t="n">
         <v>1.71</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CM12" t="n">
         <v>2.04</v>
@@ -5682,13 +5682,13 @@
         <v>1.64</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CQ12" t="n">
-        <v>5.18</v>
+        <v>5.24</v>
       </c>
       <c r="CR12" t="n">
         <v>1.61</v>
@@ -5697,7 +5697,7 @@
         <v>3.4</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CU12" t="n">
         <v>1.32</v>
@@ -5706,70 +5706,70 @@
         <v>1.62</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="DD12" t="n">
-        <v>5.99</v>
+        <v>6.04</v>
       </c>
       <c r="DE12" t="n">
         <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="DH12" t="n">
-        <v>99.66</v>
+        <v>99.14</v>
       </c>
       <c r="DI12" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="DM12" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.74</v>
+        <v>13.84</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12</v>
+        <v>12.06</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.23</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>55.14</v>
+        <v>54.89</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.8</v>
+        <v>11.67</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.63</v>
+        <v>7.5</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.17</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.95</v>
+        <v>18.06</v>
       </c>
       <c r="EB12" t="n">
         <v>1.41</v>
       </c>
       <c r="EC12" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="13">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
         <v>18</v>
@@ -5824,49 +5824,49 @@
         <v>0.06</v>
       </c>
       <c r="F13" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="G13" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="H13" t="n">
-        <v>94.06</v>
+        <v>94.94</v>
       </c>
       <c r="I13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J13" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="K13" t="n">
-        <v>5.25</v>
+        <v>5.18</v>
       </c>
       <c r="L13" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="M13" t="n">
-        <v>57.88</v>
+        <v>59.59</v>
       </c>
       <c r="N13" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="O13" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="P13" t="n">
-        <v>13.25</v>
+        <v>13.29</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.81</v>
+        <v>12.12</v>
       </c>
       <c r="R13" t="n">
-        <v>5.94</v>
+        <v>6.06</v>
       </c>
       <c r="S13" t="n">
         <v>1.12</v>
       </c>
       <c r="T13" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="U13" t="n">
         <v>0.06</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>48.06</v>
+        <v>48.41</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.25</v>
+        <v>11.06</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.94</v>
+        <v>3.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.38</v>
+        <v>21.06</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="AF13" t="n">
         <v>0.06</v>
@@ -5983,49 +5983,49 @@
         <v>2.56</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.06</v>
+        <v>9.94</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="BN13" t="n">
         <v>1.03</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.15</v>
+        <v>4.09</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.26</v>
+        <v>5.23</v>
       </c>
       <c r="BR13" t="n">
-        <v>91.18000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="BS13" t="n">
-        <v>55.88</v>
+        <v>54.29</v>
       </c>
       <c r="BT13" t="n">
-        <v>32.35</v>
+        <v>31.43</v>
       </c>
       <c r="BU13" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,19 +6034,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>23.53</v>
+        <v>22.86</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="CA13" t="n">
         <v>3.04</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CC13" t="n">
         <v>4.62</v>
@@ -6055,31 +6055,31 @@
         <v>5.42</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CH13" t="n">
         <v>1.24</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CK13" t="n">
         <v>1.63</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN13" t="n">
         <v>1.73</v>
@@ -6088,10 +6088,10 @@
         <v>1.57</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CQ13" t="n">
-        <v>5.67</v>
+        <v>5.72</v>
       </c>
       <c r="CR13" t="n">
         <v>1.63</v>
@@ -6115,7 +6115,7 @@
         <v>1.69</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.18</v>
@@ -6127,25 +6127,25 @@
         <v>1.63</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="DD13" t="n">
-        <v>6.19</v>
+        <v>6.23</v>
       </c>
       <c r="DE13" t="n">
         <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="DH13" t="n">
-        <v>90.59</v>
+        <v>91.11</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ13" t="n">
         <v>3.09</v>
@@ -6154,25 +6154,25 @@
         <v>4.32</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM13" t="n">
-        <v>51.27</v>
+        <v>52.29</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="DP13" t="n">
-        <v>13</v>
+        <v>13.03</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.03</v>
+        <v>11.2</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.47</v>
+        <v>7.48</v>
       </c>
       <c r="DS13" t="n">
         <v>0.09</v>
@@ -6184,25 +6184,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.47</v>
+        <v>45.72</v>
       </c>
       <c r="DW13" t="n">
         <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.529999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.35</v>
+        <v>6.37</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.97</v>
+        <v>20.31</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC13" t="n">
         <v>2.91</v>
@@ -9542,7 +9542,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14.76</v>
+        <v>14.71</v>
       </c>
       <c r="AR22" t="n">
         <v>9.06</v>
@@ -9773,7 +9773,7 @@
         <v>3.06</v>
       </c>
       <c r="DP22" t="n">
-        <v>13.89</v>
+        <v>13.87</v>
       </c>
       <c r="DQ22" t="n">
         <v>9.84</v>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -9542,7 +9542,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14.71</v>
+        <v>14.76</v>
       </c>
       <c r="AR22" t="n">
         <v>9.06</v>
@@ -9773,7 +9773,7 @@
         <v>3.06</v>
       </c>
       <c r="DP22" t="n">
-        <v>13.87</v>
+        <v>13.89</v>
       </c>
       <c r="DQ22" t="n">
         <v>9.84</v>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
         <v>0.12</v>
@@ -5502,49 +5502,49 @@
         <v>0.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AI12" t="n">
-        <v>93.09999999999999</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.25</v>
+        <v>3.43</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.95</v>
+        <v>46.19</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.6</v>
+        <v>14.52</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.9</v>
+        <v>11.81</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.1</v>
+        <v>10.24</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>51.4</v>
+        <v>51.14</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.85</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.55</v>
+        <v>6.67</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.15</v>
+        <v>17.95</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="BG12" t="n">
         <v>2.14</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.69</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI12" t="n">
         <v>2.14</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL12" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.44</v>
+        <v>94.59</v>
       </c>
       <c r="BS12" t="n">
-        <v>63.89</v>
+        <v>64.86</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>32.43</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>16.22</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>44.44</v>
+        <v>45.95</v>
       </c>
       <c r="BY12" t="n">
         <v>2.03</v>
@@ -5643,13 +5643,13 @@
         <v>3.08</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CD12" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CE12" t="n">
         <v>1.55</v>
@@ -5658,7 +5658,7 @@
         <v>3.59</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CH12" t="n">
         <v>1.26</v>
@@ -5667,13 +5667,13 @@
         <v>1.63</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CK12" t="n">
         <v>1.71</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CM12" t="n">
         <v>2.04</v>
@@ -5685,7 +5685,7 @@
         <v>1.51</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CQ12" t="n">
         <v>5.24</v>
@@ -5706,13 +5706,13 @@
         <v>1.62</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CX12" t="n">
         <v>1.76</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.08</v>
@@ -5721,55 +5721,55 @@
         <v>1.66</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="DD12" t="n">
-        <v>6.04</v>
+        <v>6.01</v>
       </c>
       <c r="DE12" t="n">
         <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="DH12" t="n">
-        <v>99.14</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.33</v>
+        <v>4.41</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="DM12" t="n">
-        <v>51.8</v>
+        <v>51.78</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DO12" t="n">
         <v>2.14</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.84</v>
+        <v>13.81</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.06</v>
+        <v>12</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.279999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>54.89</v>
+        <v>54.65</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.67</v>
+        <v>11.7</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.5</v>
+        <v>7.54</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.06</v>
+        <v>17.95</v>
       </c>
       <c r="EB12" t="n">
         <v>1.41</v>
       </c>
       <c r="EC12" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="13">
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D22" t="n">
         <v>17</v>
@@ -9431,49 +9431,49 @@
         <v>0.05</v>
       </c>
       <c r="F22" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="G22" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="H22" t="n">
-        <v>107.68</v>
+        <v>109.3</v>
       </c>
       <c r="I22" t="n">
         <v>0.05</v>
       </c>
       <c r="J22" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K22" t="n">
-        <v>6.53</v>
+        <v>6.45</v>
       </c>
       <c r="L22" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="M22" t="n">
-        <v>63.32</v>
+        <v>63.15</v>
       </c>
       <c r="N22" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="O22" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="P22" t="n">
-        <v>13.11</v>
+        <v>12.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.53</v>
+        <v>10.65</v>
       </c>
       <c r="R22" t="n">
-        <v>6.47</v>
+        <v>6.65</v>
       </c>
       <c r="S22" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="T22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="U22" t="n">
         <v>0.05</v>
@@ -9485,28 +9485,28 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>57.58</v>
+        <v>57.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>12.74</v>
+        <v>12.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>8.84</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>19.32</v>
+        <v>19.3</v>
       </c>
       <c r="AD22" t="n">
         <v>1.54</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -9590,70 +9590,70 @@
         <v>3.24</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="BH22" t="n">
-        <v>9.470000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.86</v>
+        <v>4.84</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.56</v>
+        <v>4.65</v>
       </c>
       <c r="BR22" t="n">
-        <v>88.89</v>
+        <v>89.19</v>
       </c>
       <c r="BS22" t="n">
-        <v>52.78</v>
+        <v>54.05</v>
       </c>
       <c r="BT22" t="n">
-        <v>33.33</v>
+        <v>32.43</v>
       </c>
       <c r="BU22" t="n">
-        <v>25</v>
+        <v>24.32</v>
       </c>
       <c r="BV22" t="n">
-        <v>16.67</v>
+        <v>16.22</v>
       </c>
       <c r="BW22" t="n">
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>36.11</v>
+        <v>37.84</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BZ22" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="CA22" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CC22" t="n">
         <v>2.78</v>
@@ -9665,10 +9665,10 @@
         <v>1.49</v>
       </c>
       <c r="CF22" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CG22" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH22" t="n">
         <v>1.31</v>
@@ -9695,10 +9695,10 @@
         <v>1.42</v>
       </c>
       <c r="CP22" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CQ22" t="n">
-        <v>4.34</v>
+        <v>4.37</v>
       </c>
       <c r="CR22" t="n">
         <v>1.52</v>
@@ -9719,13 +9719,13 @@
         <v>2.13</v>
       </c>
       <c r="CX22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CZ22" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DA22" t="n">
         <v>1.67</v>
@@ -9734,22 +9734,22 @@
         <v>1.48</v>
       </c>
       <c r="DC22" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="DD22" t="n">
-        <v>4.79</v>
+        <v>4.82</v>
       </c>
       <c r="DE22" t="n">
         <v>0.03</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="DG22" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="DH22" t="n">
-        <v>101.14</v>
+        <v>102.19</v>
       </c>
       <c r="DI22" t="n">
         <v>0.16</v>
@@ -9758,28 +9758,28 @@
         <v>3</v>
       </c>
       <c r="DK22" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="DM22" t="n">
-        <v>57.45</v>
+        <v>57.51</v>
       </c>
       <c r="DN22" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="DO22" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="DP22" t="n">
-        <v>13.89</v>
+        <v>13.78</v>
       </c>
       <c r="DQ22" t="n">
-        <v>9.84</v>
+        <v>9.92</v>
       </c>
       <c r="DR22" t="n">
-        <v>8.58</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS22" t="n">
         <v>0.05</v>
@@ -9791,19 +9791,19 @@
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>54.92</v>
+        <v>54.89</v>
       </c>
       <c r="DW22" t="n">
         <v>0.14</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.5</v>
+        <v>11.57</v>
       </c>
       <c r="DY22" t="n">
-        <v>7.39</v>
+        <v>7.48</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
       <c r="EA22" t="n">
         <v>19.03</v>
@@ -9812,7 +9812,7 @@
         <v>1.44</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="23">

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>47</v>
+        <v>47.06</v>
       </c>
       <c r="Y2" t="n">
         <v>0.12</v>
@@ -1472,7 +1472,7 @@
         <v>0.06</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="n">
         <v>2.44</v>
@@ -1484,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="n">
         <v>3.88</v>
@@ -1496,7 +1496,7 @@
         <v>44.44</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AP2" t="n">
         <v>1.44</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>43.75</v>
+        <v>44</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.12</v>
@@ -1535,10 +1535,10 @@
         <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.38</v>
+        <v>7.44</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="BD2" t="n">
         <v>21.12</v>
@@ -1547,7 +1547,7 @@
         <v>1.27</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="BG2" t="n">
         <v>2.41</v>
@@ -1703,7 +1703,7 @@
         <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="DG2" t="n">
         <v>2.84</v>
@@ -1715,7 +1715,7 @@
         <v>0.03</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="DK2" t="n">
         <v>4.31</v>
@@ -1727,7 +1727,7 @@
         <v>49.03</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="DO2" t="n">
         <v>1.5</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.38</v>
+        <v>45.53</v>
       </c>
       <c r="DW2" t="n">
         <v>0.12</v>
@@ -1760,10 +1760,10 @@
         <v>12.12</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.44</v>
+        <v>7.47</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.69</v>
+        <v>4.66</v>
       </c>
       <c r="EA2" t="n">
         <v>21.37</v>
@@ -1772,7 +1772,7 @@
         <v>1.45</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="3">
@@ -1794,7 +1794,7 @@
         <v>0.11</v>
       </c>
       <c r="F3" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="G3" t="n">
         <v>2.72</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="K3" t="n">
         <v>5.06</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>64.17</v>
+        <v>64.22</v>
       </c>
       <c r="Y3" t="n">
         <v>0.06</v>
@@ -1869,7 +1869,7 @@
         <v>1.63</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
         <v>0.11</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>60.17</v>
+        <v>60.22</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.28</v>
@@ -1944,7 +1944,7 @@
         <v>4.39</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.44</v>
+        <v>19.5</v>
       </c>
       <c r="BE3" t="n">
         <v>1.43</v>
@@ -2106,7 +2106,7 @@
         <v>0.11</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="DG3" t="n">
         <v>2.56</v>
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DK3" t="n">
         <v>5.34</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>62.17</v>
+        <v>62.22</v>
       </c>
       <c r="DW3" t="n">
         <v>0.17</v>
@@ -2169,13 +2169,13 @@
         <v>4.56</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.5</v>
+        <v>19.53</v>
       </c>
       <c r="EB3" t="n">
         <v>1.53</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.44</v>
+        <v>48.5</v>
       </c>
       <c r="Y4" t="n">
         <v>0.06</v>
@@ -2311,7 +2311,7 @@
         <v>12.56</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.44</v>
+        <v>10.38</v>
       </c>
       <c r="AS4" t="n">
         <v>8.56</v>
@@ -2542,7 +2542,7 @@
         <v>13.12</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.66</v>
+        <v>10.63</v>
       </c>
       <c r="DR4" t="n">
         <v>8.09</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.75</v>
+        <v>47.78</v>
       </c>
       <c r="DW4" t="n">
         <v>0.12</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>42.81</v>
+        <v>42.56</v>
       </c>
       <c r="Y5" t="n">
         <v>0.12</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>45.12</v>
+        <v>45.19</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.06</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>43.96</v>
+        <v>43.88</v>
       </c>
       <c r="DW5" t="n">
         <v>0.09</v>
@@ -3487,7 +3487,7 @@
         <v>0.12</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="n">
         <v>2.12</v>
@@ -3499,7 +3499,7 @@
         <v>-0.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AL7" t="n">
         <v>3.81</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>46.25</v>
+        <v>46.31</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.19</v>
@@ -3562,7 +3562,7 @@
         <v>1.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="BG7" t="n">
         <v>1.88</v>
@@ -3718,7 +3718,7 @@
         <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="DG7" t="n">
         <v>2.72</v>
@@ -3730,7 +3730,7 @@
         <v>-0.03</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="DK7" t="n">
         <v>4.6</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.97</v>
+        <v>50</v>
       </c>
       <c r="DW7" t="n">
         <v>0.22</v>
@@ -3787,7 +3787,7 @@
         <v>1.26</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="8">
@@ -3809,7 +3809,7 @@
         <v>0.19</v>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="G8" t="n">
         <v>2.57</v>
@@ -3821,7 +3821,7 @@
         <v>0.05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="K8" t="n">
         <v>5.52</v>
@@ -3833,7 +3833,7 @@
         <v>58</v>
       </c>
       <c r="N8" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>2.95</v>
@@ -3845,7 +3845,7 @@
         <v>13.57</v>
       </c>
       <c r="R8" t="n">
-        <v>8.140000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="S8" t="n">
         <v>0.48</v>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>56.05</v>
+        <v>55.95</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -3884,7 +3884,7 @@
         <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AF8" t="n">
         <v>0.06</v>
@@ -4121,7 +4121,7 @@
         <v>0.13</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="DG8" t="n">
         <v>2.35</v>
@@ -4133,7 +4133,7 @@
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="DK8" t="n">
         <v>4.89</v>
@@ -4145,7 +4145,7 @@
         <v>56</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="DO8" t="n">
         <v>2.54</v>
@@ -4157,7 +4157,7 @@
         <v>13.49</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.65</v>
+        <v>7.7</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>56.19</v>
+        <v>56.14</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
@@ -4190,7 +4190,7 @@
         <v>1.42</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="9">
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.28</v>
+        <v>52.33</v>
       </c>
       <c r="Y9" t="n">
         <v>0.11</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.88</v>
+        <v>49.94</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.06</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.15</v>
+        <v>51.21</v>
       </c>
       <c r="DW9" t="n">
         <v>0.09</v>
@@ -4726,7 +4726,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.38</v>
+        <v>10.31</v>
       </c>
       <c r="AR10" t="n">
         <v>10.69</v>
@@ -4957,7 +4957,7 @@
         <v>2.25</v>
       </c>
       <c r="DP10" t="n">
-        <v>9.94</v>
+        <v>9.91</v>
       </c>
       <c r="DQ10" t="n">
         <v>10.66</v>
@@ -5018,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="G11" t="n">
         <v>2.12</v>
@@ -5030,7 +5030,7 @@
         <v>0.18</v>
       </c>
       <c r="J11" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="K11" t="n">
         <v>3.47</v>
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>35.06</v>
+        <v>35</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -5093,13 +5093,13 @@
         <v>1.16</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AH11" t="n">
         <v>1</v>
@@ -5111,7 +5111,7 @@
         <v>0.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="AL11" t="n">
         <v>2.41</v>
@@ -5174,7 +5174,7 @@
         <v>0.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="BG11" t="n">
         <v>1.68</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>32.26</v>
+        <v>32.24</v>
       </c>
       <c r="DW11" t="n">
         <v>0.09</v>
@@ -5457,7 +5457,7 @@
         <v>12.25</v>
       </c>
       <c r="R12" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="S12" t="n">
         <v>0.88</v>
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>59.25</v>
+        <v>59.19</v>
       </c>
       <c r="Y12" t="n">
         <v>0.31</v>
@@ -5535,7 +5535,7 @@
         <v>14.52</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.81</v>
+        <v>11.76</v>
       </c>
       <c r="AS12" t="n">
         <v>10.24</v>
@@ -5766,10 +5766,10 @@
         <v>13.81</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12</v>
+        <v>11.97</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.41</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>54.65</v>
+        <v>54.62</v>
       </c>
       <c r="DW12" t="n">
         <v>0.24</v>
@@ -5905,7 +5905,7 @@
         <v>0.06</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH13" t="n">
         <v>1.72</v>
@@ -5917,7 +5917,7 @@
         <v>0.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="AL13" t="n">
         <v>3.5</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>43.17</v>
+        <v>43.28</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.06</v>
@@ -5980,7 +5980,7 @@
         <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="BG13" t="n">
         <v>1.8</v>
@@ -6136,7 +6136,7 @@
         <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DG13" t="n">
         <v>2.51</v>
@@ -6148,7 +6148,7 @@
         <v>0.14</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="DK13" t="n">
         <v>4.32</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.72</v>
+        <v>45.77</v>
       </c>
       <c r="DW13" t="n">
         <v>0.12</v>
@@ -6205,7 +6205,7 @@
         <v>1.19</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="14">
@@ -6227,7 +6227,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="G14" t="n">
         <v>2.5</v>
@@ -6239,7 +6239,7 @@
         <v>0.06</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K14" t="n">
         <v>4.88</v>
@@ -6281,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>52.25</v>
+        <v>52.31</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -6302,13 +6302,13 @@
         <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AF14" t="n">
         <v>0.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AH14" t="n">
         <v>2.06</v>
@@ -6320,7 +6320,7 @@
         <v>0.06</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AL14" t="n">
         <v>4.5</v>
@@ -6362,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>51.12</v>
+        <v>51.06</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.12</v>
@@ -6383,7 +6383,7 @@
         <v>1.23</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="BG14" t="n">
         <v>1.75</v>
@@ -6539,7 +6539,7 @@
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DG14" t="n">
         <v>2.28</v>
@@ -6551,7 +6551,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DK14" t="n">
         <v>4.69</v>
@@ -6608,7 +6608,7 @@
         <v>1.3</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="15">
@@ -6684,16 +6684,16 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>57.61</v>
+        <v>57.56</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.83</v>
+        <v>12.89</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.44</v>
+        <v>8.5</v>
       </c>
       <c r="AB15" t="n">
         <v>4.39</v>
@@ -6702,7 +6702,7 @@
         <v>21.22</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE15" t="n">
         <v>2.11</v>
@@ -6711,7 +6711,7 @@
         <v>0.06</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AH15" t="n">
         <v>1.72</v>
@@ -6723,7 +6723,7 @@
         <v>0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="AL15" t="n">
         <v>3.67</v>
@@ -6768,7 +6768,7 @@
         <v>44.17</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="BA15" t="n">
         <v>9.67</v>
@@ -6938,7 +6938,7 @@
         <v>0.03</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DG15" t="n">
         <v>1.92</v>
@@ -6950,7 +6950,7 @@
         <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="DK15" t="n">
         <v>4.28</v>
@@ -6986,16 +6986,16 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.89</v>
+        <v>50.86</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.25</v>
+        <v>11.28</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.31</v>
+        <v>7.34</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.94</v>
@@ -7029,7 +7029,7 @@
         <v>0.11</v>
       </c>
       <c r="F16" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="G16" t="n">
         <v>2.5</v>
@@ -7041,7 +7041,7 @@
         <v>0.17</v>
       </c>
       <c r="J16" t="n">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="K16" t="n">
         <v>4.94</v>
@@ -7083,10 +7083,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>60.17</v>
+        <v>60.11</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="Z16" t="n">
         <v>12.5</v>
@@ -7164,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>56.71</v>
+        <v>56.76</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.12</v>
@@ -7337,7 +7337,7 @@
         <v>0.09</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="DG16" t="n">
         <v>2.49</v>
@@ -7349,7 +7349,7 @@
         <v>0.15</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="DK16" t="n">
         <v>4.57</v>
@@ -7385,10 +7385,10 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>58.49</v>
+        <v>58.48</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="DX16" t="n">
         <v>10.68</v>
@@ -7428,7 +7428,7 @@
         <v>0.06</v>
       </c>
       <c r="F17" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="G17" t="n">
         <v>2.69</v>
@@ -7440,7 +7440,7 @@
         <v>0.12</v>
       </c>
       <c r="J17" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="K17" t="n">
         <v>4.44</v>
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>47.56</v>
+        <v>47.5</v>
       </c>
       <c r="Y17" t="n">
         <v>0.44</v>
@@ -7503,7 +7503,7 @@
         <v>1.46</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AF17" t="n">
         <v>0.06</v>
@@ -7563,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>43.24</v>
+        <v>43.18</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.06</v>
@@ -7740,7 +7740,7 @@
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="DG17" t="n">
         <v>2.19</v>
@@ -7752,7 +7752,7 @@
         <v>0.09</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="DK17" t="n">
         <v>4.15</v>
@@ -7788,7 +7788,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>45.33</v>
+        <v>45.27</v>
       </c>
       <c r="DW17" t="n">
         <v>0.24</v>
@@ -7809,7 +7809,7 @@
         <v>1.24</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -7891,10 +7891,10 @@
         <v>0.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.44</v>
+        <v>13.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.44</v>
+        <v>9.5</v>
       </c>
       <c r="AB18" t="n">
         <v>4</v>
@@ -7912,7 +7912,7 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AH18" t="n">
         <v>1.82</v>
@@ -7924,7 +7924,7 @@
         <v>0.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="AL18" t="n">
         <v>3.76</v>
@@ -7942,7 +7942,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
         <v>15.24</v>
@@ -7987,7 +7987,7 @@
         <v>1.14</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BG18" t="n">
         <v>2</v>
@@ -8139,7 +8139,7 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="DG18" t="n">
         <v>2.42</v>
@@ -8151,7 +8151,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="DK18" t="n">
         <v>4.85</v>
@@ -8169,7 +8169,7 @@
         <v>2.4</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.54</v>
+        <v>12.57</v>
       </c>
       <c r="DQ18" t="n">
         <v>14.55</v>
@@ -8193,10 +8193,10 @@
         <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.28</v>
+        <v>11.31</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.79</v>
+        <v>7.82</v>
       </c>
       <c r="DZ18" t="n">
         <v>3.48</v>
@@ -8208,7 +8208,7 @@
         <v>1.34</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="19">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>51.12</v>
+        <v>51.06</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
@@ -8586,7 +8586,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>50.92</v>
+        <v>50.89</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>
@@ -8641,7 +8641,7 @@
         <v>0.06</v>
       </c>
       <c r="J20" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="K20" t="n">
         <v>5.31</v>
@@ -8653,13 +8653,13 @@
         <v>57.94</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O20" t="n">
         <v>2.31</v>
       </c>
       <c r="P20" t="n">
-        <v>11.75</v>
+        <v>11.69</v>
       </c>
       <c r="Q20" t="n">
         <v>13.88</v>
@@ -8698,13 +8698,13 @@
         <v>4</v>
       </c>
       <c r="AC20" t="n">
-        <v>19.62</v>
+        <v>19.56</v>
       </c>
       <c r="AD20" t="n">
         <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AF20" t="n">
         <v>0.12</v>
@@ -8953,7 +8953,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ20" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="DK20" t="n">
         <v>4.5</v>
@@ -8965,13 +8965,13 @@
         <v>51.16</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO20" t="n">
         <v>1.84</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.25</v>
+        <v>12.22</v>
       </c>
       <c r="DQ20" t="n">
         <v>13.04</v>
@@ -9004,13 +9004,13 @@
         <v>3.56</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.72</v>
+        <v>17.68</v>
       </c>
       <c r="EB20" t="n">
         <v>1.26</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="21">
@@ -9086,7 +9086,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>49.81</v>
+        <v>49.75</v>
       </c>
       <c r="Y21" t="n">
         <v>0.12</v>
@@ -9167,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>41.95</v>
+        <v>42</v>
       </c>
       <c r="AZ21" t="n">
         <v>0.15</v>
@@ -9431,7 +9431,7 @@
         <v>0.05</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="G22" t="n">
         <v>2.5</v>
@@ -9443,7 +9443,7 @@
         <v>0.05</v>
       </c>
       <c r="J22" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="K22" t="n">
         <v>6.45</v>
@@ -9464,7 +9464,7 @@
         <v>12.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.65</v>
+        <v>10.6</v>
       </c>
       <c r="R22" t="n">
         <v>6.65</v>
@@ -9485,19 +9485,19 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>57.4</v>
+        <v>57.35</v>
       </c>
       <c r="Y22" t="n">
         <v>0.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>12.8</v>
+        <v>12.85</v>
       </c>
       <c r="AA22" t="n">
         <v>8.949999999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AC22" t="n">
         <v>19.3</v>
@@ -9506,7 +9506,7 @@
         <v>1.54</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
         <v>9.06</v>
       </c>
       <c r="AS22" t="n">
-        <v>10.94</v>
+        <v>11</v>
       </c>
       <c r="AT22" t="n">
         <v>1</v>
@@ -9566,7 +9566,7 @@
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>51.94</v>
+        <v>51.88</v>
       </c>
       <c r="AZ22" t="n">
         <v>0.06</v>
@@ -9581,7 +9581,7 @@
         <v>4.35</v>
       </c>
       <c r="BD22" t="n">
-        <v>18.71</v>
+        <v>18.76</v>
       </c>
       <c r="BE22" t="n">
         <v>1.32</v>
@@ -9743,7 +9743,7 @@
         <v>0.03</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="DG22" t="n">
         <v>2.19</v>
@@ -9755,7 +9755,7 @@
         <v>0.16</v>
       </c>
       <c r="DJ22" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="DK22" t="n">
         <v>5.27</v>
@@ -9776,10 +9776,10 @@
         <v>13.78</v>
       </c>
       <c r="DQ22" t="n">
-        <v>9.92</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DR22" t="n">
-        <v>8.619999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="DS22" t="n">
         <v>0.05</v>
@@ -9791,28 +9791,28 @@
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>54.89</v>
+        <v>54.84</v>
       </c>
       <c r="DW22" t="n">
         <v>0.14</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.57</v>
+        <v>11.6</v>
       </c>
       <c r="DY22" t="n">
         <v>7.48</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.08</v>
+        <v>4.11</v>
       </c>
       <c r="EA22" t="n">
-        <v>19.03</v>
+        <v>19.05</v>
       </c>
       <c r="EB22" t="n">
         <v>1.44</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="23">
@@ -9888,7 +9888,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>65.67</v>
+        <v>65.72</v>
       </c>
       <c r="Y23" t="n">
         <v>0.17</v>
@@ -9945,7 +9945,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12.18</v>
+        <v>12.29</v>
       </c>
       <c r="AR23" t="n">
         <v>12.76</v>
@@ -9969,16 +9969,16 @@
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>60.06</v>
+        <v>60.18</v>
       </c>
       <c r="AZ23" t="n">
         <v>0.12</v>
       </c>
       <c r="BA23" t="n">
-        <v>11.35</v>
+        <v>11.29</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.35</v>
+        <v>7.29</v>
       </c>
       <c r="BC23" t="n">
         <v>4</v>
@@ -9987,7 +9987,7 @@
         <v>20.59</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF23" t="n">
         <v>3.35</v>
@@ -10176,7 +10176,7 @@
         <v>2.23</v>
       </c>
       <c r="DP23" t="n">
-        <v>12.86</v>
+        <v>12.91</v>
       </c>
       <c r="DQ23" t="n">
         <v>13.37</v>
@@ -10194,16 +10194,16 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>62.95</v>
+        <v>63.03</v>
       </c>
       <c r="DW23" t="n">
         <v>0.15</v>
       </c>
       <c r="DX23" t="n">
-        <v>13.94</v>
+        <v>13.91</v>
       </c>
       <c r="DY23" t="n">
-        <v>8.710000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="DZ23" t="n">
         <v>5.23</v>
@@ -10212,7 +10212,7 @@
         <v>21.6</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="EC23" t="n">
         <v>3.06</v>
@@ -10318,10 +10318,10 @@
         <v>0.12</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" t="n">
         <v>77</v>
@@ -10330,13 +10330,13 @@
         <v>0.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AL24" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="AN24" t="n">
         <v>48.94</v>
@@ -10345,16 +10345,16 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11.75</v>
+        <v>11.88</v>
       </c>
       <c r="AR24" t="n">
-        <v>11.62</v>
+        <v>12.44</v>
       </c>
       <c r="AS24" t="n">
-        <v>10.25</v>
+        <v>10.75</v>
       </c>
       <c r="AT24" t="n">
         <v>0.44</v>
@@ -10372,25 +10372,25 @@
         <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>50.5</v>
+        <v>50.69</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.25</v>
+        <v>8.69</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.94</v>
+        <v>5.06</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.31</v>
+        <v>3.62</v>
       </c>
       <c r="BD24" t="n">
         <v>16.56</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BF24" t="n">
         <v>3</v>
@@ -10399,7 +10399,7 @@
         <v>1.71</v>
       </c>
       <c r="BH24" t="n">
-        <v>9.369999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI24" t="n">
         <v>1.71</v>
@@ -10423,10 +10423,10 @@
         <v>0.8</v>
       </c>
       <c r="BP24" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BQ24" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="BR24" t="n">
         <v>80</v>
@@ -10545,10 +10545,10 @@
         <v>0.17</v>
       </c>
       <c r="DF24" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="DG24" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="DH24" t="n">
         <v>87.97</v>
@@ -10557,13 +10557,13 @@
         <v>0</v>
       </c>
       <c r="DJ24" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DK24" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="DL24" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="DM24" t="n">
         <v>53.63</v>
@@ -10572,16 +10572,16 @@
         <v>0.86</v>
       </c>
       <c r="DO24" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="DP24" t="n">
-        <v>11.06</v>
+        <v>11.11</v>
       </c>
       <c r="DQ24" t="n">
-        <v>13.4</v>
+        <v>13.77</v>
       </c>
       <c r="DR24" t="n">
-        <v>8.43</v>
+        <v>8.65</v>
       </c>
       <c r="DS24" t="n">
         <v>0.23</v>
@@ -10593,25 +10593,25 @@
         <v>0</v>
       </c>
       <c r="DV24" t="n">
-        <v>54.14</v>
+        <v>54.23</v>
       </c>
       <c r="DW24" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="DX24" t="n">
-        <v>10.54</v>
+        <v>10.74</v>
       </c>
       <c r="DY24" t="n">
-        <v>6.37</v>
+        <v>6.43</v>
       </c>
       <c r="DZ24" t="n">
-        <v>4.17</v>
+        <v>4.31</v>
       </c>
       <c r="EA24" t="n">
         <v>19.69</v>
       </c>
       <c r="EB24" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="EC24" t="n">
         <v>2.57</v>
@@ -10666,7 +10666,7 @@
         <v>1.89</v>
       </c>
       <c r="P25" t="n">
-        <v>11.83</v>
+        <v>11.78</v>
       </c>
       <c r="Q25" t="n">
         <v>15.67</v>
@@ -10690,7 +10690,7 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>48.83</v>
+        <v>48.72</v>
       </c>
       <c r="Y25" t="n">
         <v>0.11</v>
@@ -10771,7 +10771,7 @@
         <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>46.72</v>
+        <v>46.67</v>
       </c>
       <c r="AZ25" t="n">
         <v>0.17</v>
@@ -10974,7 +10974,7 @@
         <v>1.94</v>
       </c>
       <c r="DP25" t="n">
-        <v>12.72</v>
+        <v>12.7</v>
       </c>
       <c r="DQ25" t="n">
         <v>14.73</v>
@@ -10992,7 +10992,7 @@
         <v>0</v>
       </c>
       <c r="DV25" t="n">
-        <v>47.78</v>
+        <v>47.7</v>
       </c>
       <c r="DW25" t="n">
         <v>0.14</v>
@@ -11035,7 +11035,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="G26" t="n">
         <v>2.12</v>
@@ -11047,7 +11047,7 @@
         <v>0.06</v>
       </c>
       <c r="J26" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="K26" t="n">
         <v>5.38</v>
@@ -11068,7 +11068,7 @@
         <v>12.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>13.12</v>
+        <v>13.19</v>
       </c>
       <c r="R26" t="n">
         <v>9.5</v>
@@ -11089,7 +11089,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>46.88</v>
+        <v>46.94</v>
       </c>
       <c r="Y26" t="n">
         <v>0.19</v>
@@ -11110,7 +11110,7 @@
         <v>1.41</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AF26" t="n">
         <v>0.06</v>
@@ -11343,7 +11343,7 @@
         <v>0.03</v>
       </c>
       <c r="DF26" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DG26" t="n">
         <v>2.16</v>
@@ -11355,7 +11355,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ26" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="DK26" t="n">
         <v>4.78</v>
@@ -11376,7 +11376,7 @@
         <v>13.16</v>
       </c>
       <c r="DQ26" t="n">
-        <v>13.25</v>
+        <v>13.28</v>
       </c>
       <c r="DR26" t="n">
         <v>9.119999999999999</v>
@@ -11391,7 +11391,7 @@
         <v>0</v>
       </c>
       <c r="DV26" t="n">
-        <v>44.5</v>
+        <v>44.53</v>
       </c>
       <c r="DW26" t="n">
         <v>0.12</v>
@@ -11412,7 +11412,7 @@
         <v>1.23</v>
       </c>
       <c r="EC26" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="27">
@@ -11437,7 +11437,7 @@
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>97.56</v>
@@ -11449,10 +11449,10 @@
         <v>3.12</v>
       </c>
       <c r="K27" t="n">
-        <v>5.19</v>
+        <v>5.38</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M27" t="n">
         <v>57.81</v>
@@ -11461,16 +11461,16 @@
         <v>1.06</v>
       </c>
       <c r="O27" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="P27" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="Q27" t="n">
         <v>12.69</v>
       </c>
-      <c r="Q27" t="n">
-        <v>12.56</v>
-      </c>
       <c r="R27" t="n">
-        <v>6.88</v>
+        <v>7.19</v>
       </c>
       <c r="S27" t="n">
         <v>1.06</v>
@@ -11488,25 +11488,25 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>47.25</v>
+        <v>47.06</v>
       </c>
       <c r="Y27" t="n">
         <v>0.06</v>
       </c>
       <c r="Z27" t="n">
-        <v>11.56</v>
+        <v>11.88</v>
       </c>
       <c r="AA27" t="n">
-        <v>7.56</v>
+        <v>7.69</v>
       </c>
       <c r="AB27" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="AC27" t="n">
         <v>21.31</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE27" t="n">
         <v>3</v>
@@ -11518,7 +11518,7 @@
         <v>2.06</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AI27" t="n">
         <v>80.31</v>
@@ -11533,7 +11533,7 @@
         <v>3.06</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="AN27" t="n">
         <v>43.75</v>
@@ -11542,16 +11542,16 @@
         <v>1.75</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>15.25</v>
+        <v>15.31</v>
       </c>
       <c r="AR27" t="n">
         <v>11.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>9.31</v>
+        <v>9.5</v>
       </c>
       <c r="AT27" t="n">
         <v>1.19</v>
@@ -11569,7 +11569,7 @@
         <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>44.25</v>
+        <v>44.44</v>
       </c>
       <c r="AZ27" t="n">
         <v>0.06</v>
@@ -11596,7 +11596,7 @@
         <v>1.88</v>
       </c>
       <c r="BH27" t="n">
-        <v>9.44</v>
+        <v>9.66</v>
       </c>
       <c r="BI27" t="n">
         <v>1.88</v>
@@ -11620,10 +11620,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="BP27" t="n">
-        <v>4.56</v>
+        <v>4.44</v>
       </c>
       <c r="BQ27" t="n">
-        <v>4.81</v>
+        <v>4.84</v>
       </c>
       <c r="BR27" t="n">
         <v>87.5</v>
@@ -11761,10 +11761,10 @@
         <v>3.5</v>
       </c>
       <c r="DK27" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="DL27" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DM27" t="n">
         <v>50.78</v>
@@ -11773,16 +11773,16 @@
         <v>1.4</v>
       </c>
       <c r="DO27" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="DP27" t="n">
-        <v>13.97</v>
+        <v>14.44</v>
       </c>
       <c r="DQ27" t="n">
-        <v>12.03</v>
+        <v>12.1</v>
       </c>
       <c r="DR27" t="n">
-        <v>8.1</v>
+        <v>8.35</v>
       </c>
       <c r="DS27" t="n">
         <v>0.09</v>
@@ -11800,19 +11800,19 @@
         <v>0.06</v>
       </c>
       <c r="DX27" t="n">
-        <v>9.119999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DY27" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="DZ27" t="n">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="EA27" t="n">
         <v>20.96</v>
       </c>
       <c r="EB27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="EC27" t="n">
         <v>3.38</v>
@@ -11840,7 +11840,7 @@
         <v>1.44</v>
       </c>
       <c r="G28" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="H28" t="n">
         <v>96.94</v>
@@ -11852,10 +11852,10 @@
         <v>2.31</v>
       </c>
       <c r="K28" t="n">
-        <v>5.81</v>
+        <v>5.88</v>
       </c>
       <c r="L28" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M28" t="n">
         <v>52.38</v>
@@ -11864,13 +11864,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="P28" t="n">
         <v>11.31</v>
       </c>
       <c r="Q28" t="n">
-        <v>12.19</v>
+        <v>12.25</v>
       </c>
       <c r="R28" t="n">
         <v>6.62</v>
@@ -11891,16 +11891,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>58.62</v>
+        <v>58.44</v>
       </c>
       <c r="Y28" t="n">
         <v>0.12</v>
       </c>
       <c r="Z28" t="n">
-        <v>14.56</v>
+        <v>14.62</v>
       </c>
       <c r="AA28" t="n">
-        <v>10</v>
+        <v>10.06</v>
       </c>
       <c r="AB28" t="n">
         <v>4.56</v>
@@ -11972,7 +11972,7 @@
         <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>54</v>
+        <v>54.06</v>
       </c>
       <c r="AZ28" t="n">
         <v>0.24</v>
@@ -11987,7 +11987,7 @@
         <v>4.53</v>
       </c>
       <c r="BD28" t="n">
-        <v>16.76</v>
+        <v>16.88</v>
       </c>
       <c r="BE28" t="n">
         <v>1.45</v>
@@ -11999,7 +11999,7 @@
         <v>1.48</v>
       </c>
       <c r="BH28" t="n">
-        <v>8.880000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="BI28" t="n">
         <v>1.48</v>
@@ -12023,10 +12023,10 @@
         <v>0.7</v>
       </c>
       <c r="BP28" t="n">
-        <v>4.09</v>
+        <v>4.18</v>
       </c>
       <c r="BQ28" t="n">
-        <v>4.52</v>
+        <v>4.58</v>
       </c>
       <c r="BR28" t="n">
         <v>72.73</v>
@@ -12148,7 +12148,7 @@
         <v>1.79</v>
       </c>
       <c r="DG28" t="n">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="DH28" t="n">
         <v>91.48</v>
@@ -12160,10 +12160,10 @@
         <v>2.88</v>
       </c>
       <c r="DK28" t="n">
-        <v>5.21</v>
+        <v>5.25</v>
       </c>
       <c r="DL28" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="DM28" t="n">
         <v>48.7</v>
@@ -12172,13 +12172,13 @@
         <v>1.03</v>
       </c>
       <c r="DO28" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DP28" t="n">
         <v>11.79</v>
       </c>
       <c r="DQ28" t="n">
-        <v>10.88</v>
+        <v>10.91</v>
       </c>
       <c r="DR28" t="n">
         <v>7.24</v>
@@ -12193,22 +12193,22 @@
         <v>0</v>
       </c>
       <c r="DV28" t="n">
-        <v>56.24</v>
+        <v>56.18</v>
       </c>
       <c r="DW28" t="n">
         <v>0.18</v>
       </c>
       <c r="DX28" t="n">
-        <v>13.63</v>
+        <v>13.66</v>
       </c>
       <c r="DY28" t="n">
-        <v>9.09</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ28" t="n">
         <v>4.54</v>
       </c>
       <c r="EA28" t="n">
-        <v>16.76</v>
+        <v>16.82</v>
       </c>
       <c r="EB28" t="n">
         <v>1.53</v>
@@ -12317,7 +12317,7 @@
         <v>0.11</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AH29" t="n">
         <v>2.63</v>
@@ -12329,7 +12329,7 @@
         <v>0.16</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="AL29" t="n">
         <v>3.89</v>
@@ -12341,13 +12341,13 @@
         <v>48.16</v>
       </c>
       <c r="AO29" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP29" t="n">
         <v>1.26</v>
       </c>
       <c r="AQ29" t="n">
-        <v>12.79</v>
+        <v>12.63</v>
       </c>
       <c r="AR29" t="n">
         <v>10.47</v>
@@ -12392,7 +12392,7 @@
         <v>1.27</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="BG29" t="n">
         <v>1.74</v>
@@ -12548,7 +12548,7 @@
         <v>0.15</v>
       </c>
       <c r="DF29" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="DG29" t="n">
         <v>2.23</v>
@@ -12560,7 +12560,7 @@
         <v>0.17</v>
       </c>
       <c r="DJ29" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="DK29" t="n">
         <v>3.89</v>
@@ -12572,13 +12572,13 @@
         <v>47.09</v>
       </c>
       <c r="DN29" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="DO29" t="n">
         <v>1.65</v>
       </c>
       <c r="DP29" t="n">
-        <v>12.83</v>
+        <v>12.74</v>
       </c>
       <c r="DQ29" t="n">
         <v>12.31</v>
@@ -12617,7 +12617,7 @@
         <v>1.25</v>
       </c>
       <c r="EC29" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="30">
@@ -13096,7 +13096,7 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>57.94</v>
+        <v>57.82</v>
       </c>
       <c r="Y31" t="n">
         <v>0.29</v>
@@ -13398,7 +13398,7 @@
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>54.39</v>
+        <v>54.33</v>
       </c>
       <c r="DW31" t="n">
         <v>0.3</v>

--- a/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
+++ b/data/teams/leagues/Averages_Argentina_Primera_División_2025.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
